--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -10,53 +10,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>模块</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>寄存器地址</t>
+          <t>Register Address</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>寄存器名</t>
+          <t>Register Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>访问属性</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>复位值</t>
+          <t>Reset Value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>位段</t>
+          <t>Bit Field</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>字段名</t>
+          <t>Field Name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -98,12 +98,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IP版本号</t>
+          <t>IP version</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>固定返回32'h0001_0000</t>
+          <t>Returns fixed value 32'h0001_0000</t>
         </is>
       </c>
     </row>
@@ -145,12 +145,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL日期</t>
+          <t>RTL date</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>固定返回32'h2026_0406</t>
+          <t>Returns fixed value 32'h2026_0406</t>
         </is>
       </c>
     </row>
@@ -192,12 +192,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>编码UBWC使能</t>
+          <t>Enable UBWC encoding</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>建议作为tile地址配置组最后写入; 写该寄存器会产生tile_addr_gen_cfg_vld脉冲</t>
+          <t>Recommended as the final write in the tile address configuration group</t>
         </is>
       </c>
     </row>
@@ -239,12 +239,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>一级bank swizzle使能</t>
+          <t>Level-1 bank swizzle enable</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -286,12 +286,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>二级bank swizzle使能</t>
+          <t>Level-2 bank swizzle enable</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -333,12 +333,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>三级bank swizzle使能</t>
+          <t>Level-3 bank swizzle enable</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -380,12 +380,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>最高bank bit配置</t>
+          <t>Highest bank bit configuration</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -427,12 +427,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>bank spread使能</t>
+          <t>Bank spread enable</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -474,12 +474,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4-line tile格式使能</t>
+          <t>4-line tile format enable</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>建议先写本寄存器再写REG_TILE_CFG0提交</t>
+          <t>Recommended to write this register before committing REG_TILE_CFG0</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy格式选择</t>
+          <t>RGBA 2:1 lossy format select</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pitch</t>
+          <t>tile_pitch</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>tile pitch配置</t>
+          <t>Tile pitch configuration</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>代码中实际有效位宽为11bit; o_pitch高位补0</t>
+          <t>The effective width in code is 11 bits</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>编码CI输入类型</t>
+          <t>Encoded CI input type</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>建议作为CI配置组最后写入; 写该寄存器会产生o_enc_ci_vld脉冲</t>
+          <t>Recommended as the final write in the CI configuration group</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>编码CI alen配置</t>
+          <t>Encoded CI alen configuration</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>编码CI格式</t>
+          <t>Encoded CI format</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -751,17 +751,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>enc_ci_forced_pcm</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>强制PCM模式</t>
+          <t>Unused forced PCM configuration bit</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Forced PCM is generated dynamically by the OTF path</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>编码CI sideband配置</t>
+          <t>Encoded CI sideband configuration</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>位宽由SB_WIDTH参数决定</t>
+          <t>Width is determined by the SB_WIDTH parameter</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>编码CI lossy使能</t>
+          <t>Encoded CI lossy enable</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UBWC CI配置0</t>
+          <t>UBWC CI configuration 0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UBWC CI配置1</t>
+          <t>UBWC CI configuration 1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UBWC CI配置2</t>
+          <t>UBWC CI configuration 2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>UBWC CI配置3</t>
+          <t>UBWC CI configuration 3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>UBWC CI配置4</t>
+          <t>UBWC CI configuration 4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>UBWC CI配置5</t>
+          <t>UBWC CI configuration 5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>UBWC CI配置6</t>
+          <t>UBWC CI configuration 6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>UBWC CI配置7</t>
+          <t>UBWC CI configuration 7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>UBWC CI配置8</t>
+          <t>UBWC CI configuration 8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>UBWC CI配置9</t>
+          <t>UBWC CI configuration 9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>UBWC CI配置10</t>
+          <t>UBWC CI configuration 10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>UBWC CI配置11</t>
+          <t>UBWC CI configuration 11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>输入OTF格式</t>
+          <t>Input OTF format</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>建议作为OTF配置组最后写入; 写该寄存器会产生o_otf_cfg_vld脉冲</t>
+          <t>Recommended as the final write in the OTF configuration group</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>输入图像宽度像素</t>
+          <t>Input image width in pixels</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>输入图像高度像素</t>
+          <t>Input image height in pixels</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>tile宽度像素</t>
+          <t>Tile width in pixels</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>tile高度像素</t>
+          <t>Tile height in pixels</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A面tile列数</t>
+          <t>A-plane tile column count</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>B面tile列数</t>
+          <t>B-plane tile column count</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Y面压缩数据基地址低32位</t>
+          <t>Low 32 bits of the Y-plane compressed data base address</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Y面压缩数据基地址高32位</t>
+          <t>High 32 bits of the Y-plane compressed data base address</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>UV或RGBA面压缩数据基地址低32位</t>
+          <t>Low 32 bits of the UV or RGBA-plane compressed data base address</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>UV或RGBA面压缩数据基地址高32位</t>
+          <t>High 32 bits of the UV or RGBA-plane compressed data base address</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Y面metadata基地址低32位</t>
+          <t>Low 32 bits of the Y-plane metadata base address</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Y面metadata基地址高32位</t>
+          <t>High 32 bits of the Y-plane metadata base address</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>UV或RGBA面metadata基地址低32位</t>
+          <t>Low 32 bits of the UV or RGBA-plane metadata base address</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>UV或RGBA面metadata基地址高32位</t>
+          <t>High 32 bits of the UV or RGBA-plane metadata base address</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>metadata有效区域宽度像素</t>
+          <t>Metadata active-area width in pixels</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>写0表示沿用整帧宽度</t>
+          <t>Writing 0 means using the full-frame width</t>
         </is>
       </c>
     </row>
@@ -2213,70 +2213,728 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>metadata有效区域高度像素</t>
+          <t>Metadata active-area height in pixels</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>写0表示沿用整帧高度</t>
+          <t>Writing 0 means using the full-frame height</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x0054</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>REG_META_PITCH</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>meta_data_plane_pitch</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metadata plane pitch in bytes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Program this separately from the pixel-data pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>enc_idle</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Encoder core idle status</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>enc_error</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Encoder core error status</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>otf_to_tile_busy</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OTF-to-tile busy status</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>otf_to_tile_overflow</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OTF-to-tile FIFO overflow status</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>otf_err_bline</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OTF input bad-line error status</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>otf_err_bframe</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>OTF input bad-frame error status</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>meta_err_0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Metadata generator error 0 status</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Currently tied low</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>meta_err_1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Metadata generator error 1 status</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Currently tied low</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x0058</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>REG_STATUS0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>frame_done</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Encoder frame done status</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Live frame done input from wrapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x005c</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>REG_STATUS1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>7:0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>stage_done</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Encoder stage done bitmap</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RW/W1P</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>irq_enable</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>IRQ enable</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Defaults to 1 after reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>irq_clear</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>IRQ clear pulse</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Writing 1 generates an irq_clear pulse in the encoder clock domain; readback is 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>irq_pending</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>IRQ pending status</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I47"/>
+  <autoFilter ref="A1:I61"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>模块</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>寄存器地址</t>
+          <t>Register Address</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>寄存器名</t>
+          <t>Register Name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>访问属性</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>复位值</t>
+          <t>Reset Value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>位段</t>
+          <t>Bit Field</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>字段名</t>
+          <t>Field Name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2976,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IP版本号</t>
+          <t>IP version</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>固定返回32'h0001_0000</t>
+          <t>Returns fixed value 32'h0001_0000</t>
         </is>
       </c>
     </row>
@@ -2365,12 +3023,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL日期</t>
+          <t>RTL date</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>固定返回32'h2026_0403</t>
+          <t>Returns fixed value 32'h2026_0403</t>
         </is>
       </c>
     </row>
@@ -2412,7 +3070,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>一级bank swizzle使能</t>
+          <t>Level-1 bank swizzle enable</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2459,7 +3117,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>二级bank swizzle使能</t>
+          <t>Level-2 bank swizzle enable</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2506,7 +3164,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>三级bank swizzle使能</t>
+          <t>Level-3 bank swizzle enable</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2553,7 +3211,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>最高bank bit配置</t>
+          <t>Highest bank bit configuration</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2600,7 +3258,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>bank spread使能</t>
+          <t>Bank spread enable</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2647,7 +3305,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4-line tile格式使能</t>
+          <t>4-line tile format enable</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2694,7 +3352,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy格式选择</t>
+          <t>RGBA 2:1 lossy format select</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2741,7 +3399,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>tile pitch配置</t>
+          <t>Tile pitch configuration</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2788,7 +3446,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CI输入类型</t>
+          <t>CI input type</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2835,12 +3493,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI sideband配置</t>
+          <t>CI sideband configuration</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>位宽由SB_WIDTH参数决定</t>
+          <t>Width is determined by the SB_WIDTH parameter</t>
         </is>
       </c>
     </row>
@@ -2882,7 +3540,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CI lossy使能</t>
+          <t>CI lossy enable</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2929,7 +3587,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CI alpha mode配置</t>
+          <t>CI alpha mode configuration</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2976,12 +3634,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ubwc_dec_vivo_top使能</t>
+          <t>ubwc_dec_vivo_top enable</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>复位后默认1</t>
+          <t>Defaults to 1 after reset</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3681,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>vivo子模块软复位</t>
+          <t>VIVO submodule soft reset</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>可用于单独清空vivo内部状态</t>
+          <t>Can be used to independently clear VIVO internal state</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3728,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>启动脉冲位</t>
+          <t>Start pulse bit</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>写1会翻转start toggle并在AXI域产生frame_start_pulse_axi; 读回固定为0; 建议最后写</t>
+          <t>Writing 1 toggles the start toggle and generates frame_start_pulse_axi in the AXI domain; readback is fixed to 0; recommended as the final write</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3775,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>metadata/base格式配置</t>
+          <t>Metadata/base format configuration</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>通常与start在同一次写操作中一起下发</t>
+          <t>Usually issued with start in the same write</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3817,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_uv[31:0]</t>
+          <t>meta_base_addr_rgba_y[31:0]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RGBA或UV metadata基地址低32位</t>
+          <t>Low 32 bits of the RGBA or Y metadata base address</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3206,17 +3864,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_uv[63:32]</t>
+          <t>meta_base_addr_rgba_y[63:32]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RGBA或UV metadata基地址高32位</t>
+          <t>High 32 bits of the RGBA or Y metadata base address</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3911,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>meta_base_addr_y[31:0]</t>
+          <t>meta_base_addr_uv[31:0]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Y metadata基地址低32位</t>
+          <t>Low 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3300,17 +3958,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>meta_base_addr_y[63:32]</t>
+          <t>meta_base_addr_uv[63:32]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Y metadata基地址高32位</t>
+          <t>High 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -3352,7 +4010,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>metadata横向tile数量</t>
+          <t>Metadata tile count in the horizontal direction</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3399,7 +4057,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>metadata纵向tile数量</t>
+          <t>Metadata tile count in the vertical direction</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3446,7 +4104,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>输出图像有效宽度像素</t>
+          <t>Valid output image width in pixels</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3493,7 +4151,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>输出OTF格式</t>
+          <t>Output OTF format</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3916,7 +4574,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>RGBA或UV tile基地址低32位</t>
+          <t>Low 32 bits of the RGBA or UV tile base address</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3963,12 +4621,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>RGBA或UV tile基地址高32位</t>
+          <t>High 32 bits of the RGBA or UV tile base address</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4668,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Y tile基地址低32位</t>
+          <t>Low 32 bits of the Y tile base address</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4057,12 +4715,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Y tile基地址高32位</t>
+          <t>High 32 bits of the Y tile base address</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AXI_AW=64时完整组成64bit地址</t>
+          <t>Forms the full 64-bit address when AXI_AW=64</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4747,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4104,12 +4762,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>当前帧是否处于active状态</t>
+          <t>Whether the current frame is active</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>启动后置1; 当前帧全部完成后清0</t>
+          <t>Set to 1 after start; cleared to 0 when the current frame fully completes</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4794,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4151,7 +4809,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>metadata读取阶段busy</t>
+          <t>Metadata read stage busy</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4183,7 +4841,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4198,7 +4856,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>tile读取阶段busy</t>
+          <t>Tile read stage busy</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4230,7 +4888,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4277,7 +4935,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4292,7 +4950,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>tile_to_otf阶段busy</t>
+          <t>tile_to_otf stage busy</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4324,7 +4982,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4339,12 +4997,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>当前所有busy输入均为0</t>
+          <t>All current busy inputs are 0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>启动前和结束后都可能为1</t>
+          <t>May be 1 before start and after completion</t>
         </is>
       </c>
     </row>
@@ -4371,7 +5029,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>动态</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4386,12 +5044,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>当前无busy且frame_active=0</t>
+          <t>No current busy and frame_active=0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>建议与STATUS1[4]联合判断本帧结束</t>
+          <t>Recommended to combine with STATUS1[4] to judge frame completion</t>
         </is>
       </c>
     </row>
@@ -4433,12 +5091,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>metadata阶段已完成</t>
+          <t>Metadata stage completed</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>新一帧start时清零</t>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4480,12 +5138,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>tile阶段已完成</t>
+          <t>Tile stage completed</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>新一帧start时清零</t>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4527,12 +5185,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>vivo阶段已完成</t>
+          <t>VIVO stage completed</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>新一帧start时清零</t>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4574,12 +5232,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>OTF输出阶段已完成</t>
+          <t>OTF output stage completed</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>新一帧start时清零</t>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4621,12 +5279,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>整帧完成标志</t>
+          <t>Full-frame completion flag</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>最推荐的软件轮询位</t>
+          <t>Most recommended software polling bit</t>
         </is>
       </c>
     </row>
@@ -4668,12 +5326,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>本帧期间metadata阶段曾经进入busy</t>
+          <t>Metadata stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>用于避免未启动就误判done</t>
+          <t>Used to avoid falsely judging done before start</t>
         </is>
       </c>
     </row>
@@ -4715,12 +5373,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>本帧期间tile阶段曾经进入busy</t>
+          <t>Tile stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -4762,12 +5420,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>本帧期间vivo阶段曾经进入busy</t>
+          <t>VIVO stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -4809,17 +5467,252 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>本帧期间otf阶段曾经进入busy</t>
+          <t>OTF stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>Same as above</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x005c</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STATUS2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>vivo_idle_bits</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Raw ubwc_dec_vivo_top idle bitmap</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Passed through as o_idle[6:0] for software debug</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STATUS3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>6:0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>vivo_error_bits</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Raw ubwc_dec_vivo_top error bitmap</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Passed through as o_error[6:0] for software debug</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>APB_ADDR_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RW/W1P</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>irq_enable</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>IRQ enable</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Defaults to 1 after reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>APB_ADDR_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>irq_clear</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>IRQ clear pulse</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Writing 1 generates an irq_clear pulse in the AXI clock domain; readback is 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>APB_ADDR_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>irq_pending</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>IRQ pending status</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I55"/>
+  <autoFilter ref="A1:I60"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -4,57 +4,125 @@
   <sheets>
     <sheet name="ubwc_enc_apb" sheetId="1" r:id="rId1"/>
     <sheet name="ubwc_dec_apb" sheetId="2" r:id="rId2"/>
+    <sheet name="Overview" sheetId="3" r:id="rId3"/>
+    <sheet name="Programming_Guide" sheetId="4" r:id="rId4"/>
+    <sheet name="Address_Rules" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border/>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyFill="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I61"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
+    <col min="9" max="9" width="90" customWidth="1"/>
+  </cols>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Register Address</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Register Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Reset Value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Bit Field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -66,7 +134,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>0x0000</t>
         </is>
@@ -81,7 +149,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>0x00010000</t>
         </is>
@@ -113,7 +181,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>0x0004</t>
         </is>
@@ -128,7 +196,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>0x20260406</t>
         </is>
@@ -160,7 +228,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -175,7 +243,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -207,7 +275,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -222,7 +290,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -254,7 +322,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -269,7 +337,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -301,7 +369,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -316,7 +384,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -348,7 +416,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -363,7 +431,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -395,7 +463,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -410,7 +478,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -442,7 +510,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>0x000c</t>
         </is>
@@ -457,7 +525,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -479,7 +547,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Recommended to write this register before committing REG_TILE_CFG0</t>
+          <t>Program by format: RGBA8888/RGBA1010102=1; YUV420_8/YUV420_10=0. Recommended to write this register before committing REG_TILE_CFG0.</t>
         </is>
       </c>
     </row>
@@ -489,7 +557,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>0x000c</t>
         </is>
@@ -504,7 +572,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -536,7 +604,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>0x000c</t>
         </is>
@@ -551,7 +619,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -568,12 +636,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tile pitch configuration</t>
+          <t>Tile pitch in 16-byte units</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>The effective width in code is 11 bits</t>
+          <t>Write pitch_reg=align_up(width*bytes_per_pixel, tile_w*4*bytes_per_pixel)/16. bytes_per_pixel: RGBA8888=4, RGBA1010102=4, YUV420_8=1, YUV420_10=2. This register value is in 16-byte units, not bytes; effective field width is 11 bits. Example NV12 1996x1074: align_up(1996*1,32*4*1)=2048 bytes, tile_pitch=2048/16=128.</t>
         </is>
       </c>
     </row>
@@ -583,7 +651,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -598,7 +666,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -620,7 +688,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the CI configuration group</t>
+          <t>Encoding: 0=linear data, 1=tiled data. Fixed value for current encoder path: software should write 1. Recommended as the final write in the CI configuration group.</t>
         </is>
       </c>
     </row>
@@ -630,7 +698,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -645,7 +713,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -667,7 +735,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Fixed value. Software should write 3'd7.</t>
         </is>
       </c>
     </row>
@@ -677,7 +745,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -692,7 +760,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -704,17 +772,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>enc_ci_format</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Encoded CI format</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Reserved. Software should write 0; current encoder format is configured by REG_OTF_CFG0.otf_cfg_format.</t>
         </is>
       </c>
     </row>
@@ -724,7 +792,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -739,7 +807,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -756,12 +824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Unused forced PCM configuration bit</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Forced PCM is generated dynamically by the OTF path</t>
+          <t>Reserved. Software should write 0; forced PCM is generated dynamically by the OTF path.</t>
         </is>
       </c>
     </row>
@@ -771,7 +839,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>0x0014</t>
         </is>
@@ -786,7 +854,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -803,12 +871,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Encoded CI sideband configuration</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Width is determined by the SB_WIDTH parameter</t>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -818,7 +886,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>0x0014</t>
         </is>
@@ -833,7 +901,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -865,7 +933,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -880,7 +948,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -897,12 +965,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 0</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -912,7 +980,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -927,7 +995,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -944,12 +1012,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 1</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -959,7 +1027,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -974,7 +1042,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -991,12 +1059,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 2</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1074,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1021,7 +1089,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1038,12 +1106,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 3</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1121,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1068,7 +1136,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1085,12 +1153,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 4</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1168,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1115,7 +1183,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1132,12 +1200,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 5</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1215,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1162,7 +1230,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1179,12 +1247,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 6</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1262,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1209,7 +1277,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1226,12 +1294,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 7</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1309,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1256,7 +1324,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1273,12 +1341,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 8</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1356,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>0x0018</t>
         </is>
@@ -1303,7 +1371,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1320,12 +1388,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 9</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1403,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>0x001c</t>
         </is>
@@ -1350,7 +1418,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1367,12 +1435,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 10</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1450,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>0x001c</t>
         </is>
@@ -1397,7 +1465,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1414,12 +1482,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>UBWC CI configuration 11</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1497,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>0x0020</t>
         </is>
@@ -1444,7 +1512,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1466,7 +1534,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the OTF configuration group</t>
+          <t>Recommended as the final write in the OTF configuration group. Format code: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1544,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>0x0024</t>
         </is>
@@ -1491,7 +1559,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1513,7 +1581,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t>Software should use this width to calculate tile columns: ceil(width / tile_w).</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1591,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>0x0024</t>
         </is>
@@ -1538,7 +1606,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1560,7 +1628,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>Program stored/input frame height. For YUV420, UV plane uses half-height internally.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1638,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>0x0028</t>
         </is>
@@ -1585,7 +1653,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1607,7 +1675,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>Program by format: RGBA8888/RGBA1010102=16; YUV420_8/YUV420_10=32.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1685,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>0x0028</t>
         </is>
@@ -1632,7 +1700,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1654,7 +1722,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t/>
+          <t>Program by format: RGBA8888/RGBA1010102=4; YUV420_8/YUV420_10=8.</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1732,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>0x002c</t>
         </is>
@@ -1679,7 +1747,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1691,17 +1759,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>otf_cfg_a_tile_cols</t>
+          <t>otf_cfg_y_tile_cols</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A-plane tile column count</t>
+          <t>Y tile column count</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>Program by format: RGBA formats=ceil(width/16); YUV formats Y=ceil(width/32).</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1779,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>0x002c</t>
         </is>
@@ -1726,7 +1794,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1738,17 +1806,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>otf_cfg_b_tile_cols</t>
+          <t>otf_cfg_uv_tile_cols</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>B-plane tile column count</t>
+          <t>UV tile column count</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>Program by format: RGBA formats=0; YUV formats UV=ceil(width/32).</t>
         </is>
       </c>
     </row>
@@ -1758,14 +1826,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>0x0030</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_LO</t>
+          <t>REG_META_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1773,7 +1841,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1785,17 +1853,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>meta_y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y-plane compressed data base address</t>
+          <t>Low 32 bits of the Y metadata base address</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>For RGBA formats, use this slot for RGBA metadata. For YUV formats, program Y metadata start. Example NV12 1996x1074 base=0xA00000: Y meta_base=0xA00000, Y meta_pitch=64, Y meta_size=0x3000.</t>
         </is>
       </c>
     </row>
@@ -1805,14 +1873,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>0x0034</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_HI</t>
+          <t>REG_META_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1820,7 +1888,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1832,12 +1900,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>meta_y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y-plane compressed data base address</t>
+          <t>High 32 bits of the Y metadata base address</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1852,14 +1920,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>0x0038</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_LO</t>
+          <t>REG_TILE_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1867,7 +1935,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1879,17 +1947,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV or RGBA-plane compressed data base address</t>
+          <t>Low 32 bits of the Y compressed data base address</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>For RGBA formats, use this slot for RGBA compressed data. For YUV formats, program Y pixel/tile data start. Example NV12 1996x1074: Y tile_base=0xA03000.</t>
         </is>
       </c>
     </row>
@@ -1899,14 +1967,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>0x003c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_HI</t>
+          <t>REG_TILE_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1914,7 +1982,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1926,12 +1994,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV or RGBA-plane compressed data base address</t>
+          <t>High 32 bits of the Y compressed data base address</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1946,14 +2014,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>0x0040</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_LO</t>
+          <t>REG_META_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1961,7 +2029,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -1973,17 +2041,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y-plane metadata base address</t>
+          <t>Low 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV_meta_base=0xC23000.</t>
         </is>
       </c>
     </row>
@@ -1993,14 +2061,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>0x0044</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_HI</t>
+          <t>REG_META_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2008,7 +2076,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2020,12 +2088,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y-plane metadata base address</t>
+          <t>High 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2040,14 +2108,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>0x0048</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_LO</t>
+          <t>REG_TILE_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2055,7 +2123,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2067,17 +2135,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV or RGBA-plane metadata base address</t>
+          <t>Low 32 bits of the UV compressed data base address</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV tile_base=0xC25000.</t>
         </is>
       </c>
     </row>
@@ -2087,14 +2155,14 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>0x004c</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_HI</t>
+          <t>REG_TILE_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2102,7 +2170,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2114,17 +2182,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV or RGBA-plane metadata base address</t>
+          <t>High 32 bits of the UV compressed data base address</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Forms the full 64-bit address and commits the current frame address set</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2202,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>0x0050</t>
         </is>
@@ -2149,7 +2217,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2181,7 +2249,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>0x0050</t>
         </is>
@@ -2196,7 +2264,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2218,7 +2286,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Writing 0 means using the full-frame height</t>
+          <t>Program metadata active height in pixels.</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2296,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>0x0054</t>
         </is>
@@ -2243,7 +2311,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -2260,12 +2328,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metadata plane pitch in bytes</t>
+          <t>Metadata plane pitch</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Program this separately from the pixel-data pitch</t>
+          <t>Write meta_data_plane_pitch=align_up((align_up(width, tile_w*4)+tile_w-1)/tile_w, 64), matching ubwc_demo.cpp. Current encoder meta address path uses meta_data_plane_pitch&lt;&lt;4 as byte stride. Example NV12 1996x1074 Y plane: align_up((align_up(1996,128)+32-1)/32,64)=64. UV plane example from contiguous layout also uses meta_pitch=64.</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2343,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2322,7 +2390,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2369,7 +2437,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2416,7 +2484,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2463,7 +2531,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2510,7 +2578,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2557,7 +2625,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2604,7 +2672,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2651,7 +2719,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
@@ -2698,7 +2766,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>0x005c</t>
         </is>
@@ -2745,7 +2813,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>0x0060</t>
         </is>
@@ -2760,7 +2828,7 @@
           <t>RW/W1P</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>0x00000001</t>
         </is>
@@ -2792,7 +2860,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>0x0060</t>
         </is>
@@ -2807,7 +2875,7 @@
           <t>W1P</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>0x00000001</t>
         </is>
@@ -2839,7 +2907,7 @@
           <t>ubwc_enc_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>0x0060</t>
         </is>
@@ -2888,51 +2956,62 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I64"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
+    <col min="9" max="9" width="90" customWidth="1"/>
+  </cols>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Register Address</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Register Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Reset Value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Bit Field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2944,7 +3023,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>0x0000</t>
         </is>
@@ -2959,7 +3038,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>0x00010000</t>
         </is>
@@ -2991,7 +3070,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>0x0004</t>
         </is>
@@ -3006,7 +3085,7 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>0x20260403</t>
         </is>
@@ -3038,7 +3117,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3053,7 +3132,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -3075,7 +3154,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>Software default writes 0. Combined bank swizzle default [2:0]=3'b110.</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3164,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3100,7 +3179,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -3122,7 +3201,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t/>
+          <t>Software default writes 1. Combined bank swizzle default [2:0]=3'b110.</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3211,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3147,7 +3226,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -3169,7 +3248,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t/>
+          <t>Software default writes 1. Combined bank swizzle default [2:0]=3'b110.</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3258,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3194,7 +3273,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -3226,7 +3305,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3241,7 +3320,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -3263,7 +3342,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t>Software default writes 1.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3352,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>0x0008</t>
         </is>
@@ -3288,29 +3367,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tile_cfg_4line_format</t>
+          <t>tile_cfg_is_lossy_rgba_2_1_format</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4-line tile format enable</t>
+          <t>RGBA 2:1 lossy format select</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t/>
+          <t>Only applies to RGBA8888 metadata/tile address path. 0=normal RGBA/lossless layout, 1=RGBA8888 lossy 2:1 layout. When 1, decoder halves the effective tile_y for address calculation, adds a 128-byte offset for odd tile_y, disables bank spread for this path, and treats 256-byte metadata payload as 128 bytes.</t>
         </is>
       </c>
     </row>
@@ -3320,14 +3399,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0x0008</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG0</t>
+          <t>APB_ADDR_TILE_CFG1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3335,29 +3414,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11:0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tile_cfg_is_lossy_rgba_2_1_format</t>
+          <t>tile_cfg_pitch</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy format select</t>
+          <t>Tile pitch configuration</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t>Tile surface pitch in 16-byte units. Program tile_cfg_pitch=align_up(width*bpp, tile_w*4*bpp)/16. bpp: RGBA8888/RGBA1010102=4, YUV420_8=1, YUV420_10=2. tile_w: RGBA=16, YUV=32. RTL uses tile_cfg_pitch&lt;&lt;4 as byte pitch. Example NV12 1996x1074: align_up(1996*1,32*4*1)=2048 bytes, tile_cfg_pitch=2048/16=128.</t>
         </is>
       </c>
     </row>
@@ -3367,14 +3446,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0x000c</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG1</t>
+          <t>APB_ADDR_TILE_CFG2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3382,29 +3461,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tile_cfg_pitch</t>
+          <t>tile_cfg_ci_input_type</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tile pitch configuration</t>
+          <t>CI input type</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t>0=linear data, 1=tiled data. Software default writes 1.</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3493,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -3429,29 +3508,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_input_type</t>
+          <t>tile_cfg_ci_lossy</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CI input type</t>
+          <t>CI lossy enable</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t/>
+          <t>Software writes 1 for lossy format and 0 for lossless format.</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3540,7 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>0x0010</t>
         </is>
@@ -3476,29 +3555,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SB_WIDTH:1</t>
+          <t>10:9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_sb</t>
+          <t>tile_cfg_ci_alpha_mode</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI sideband configuration</t>
+          <t>CI alpha mode configuration</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Width is determined by the SB_WIDTH parameter</t>
+          <t>Reserved. Software should write 0.</t>
         </is>
       </c>
     </row>
@@ -3508,14 +3587,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0x0010</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG2</t>
+          <t>APB_ADDR_VIVO_CFG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3523,29 +3602,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_lossy</t>
+          <t>vivo_ubwc_en</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CI lossy enable</t>
+          <t>ubwc_dec_vivo_top enable</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t>Defaults to 1 after reset</t>
         </is>
       </c>
     </row>
@@ -3555,14 +3634,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0x0010</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG2</t>
+          <t>APB_ADDR_VIVO_CFG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3570,29 +3649,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10:9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_alpha_mode</t>
+          <t>vivo_sreset</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CI alpha mode configuration</t>
+          <t>VIVO submodule soft reset</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t/>
+          <t>Can be used to independently clear VIVO internal state</t>
         </is>
       </c>
     </row>
@@ -3602,14 +3681,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0x0014</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APB_ADDR_VIVO_CFG</t>
+          <t>APB_ADDR_OTF_CFG0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3617,29 +3696,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>vivo_ubwc_en</t>
+          <t>otf_cfg_img_width</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ubwc_dec_vivo_top enable</t>
+          <t>Valid output image width in pixels</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Program active image width in pixels. Used to limit line unpacking: RGBA words=ceil(width/4), YUV420_8/NV12 words=ceil(width/16), YUV420_10/P010 words=ceil(width/8).</t>
         </is>
       </c>
     </row>
@@ -3649,14 +3728,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0x0014</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APB_ADDR_VIVO_CFG</t>
+          <t>APB_ADDR_OTF_CFG0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3664,29 +3743,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>vivo_sreset</t>
+          <t>otf_cfg_format</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>VIVO submodule soft reset</t>
+          <t>Output OTF format</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Can be used to independently clear VIVO internal state</t>
+          <t>Frame-level output format. Codes: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010. Also drives meta_base_format.</t>
         </is>
       </c>
     </row>
@@ -3696,44 +3775,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0x0018</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG0</t>
+          <t>APB_ADDR_OTF_CFG1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>W1P/RW</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>meta_start</t>
+          <t>otf_cfg_h_total</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Start pulse bit</t>
+          <t>OTF H_TOTAL</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Writing 1 toggles the start toggle and generates frame_start_pulse_axi in the AXI domain; readback is fixed to 0; recommended as the final write</t>
+          <t>Horizontal total in pixels. RTL converts to OTF beats with ceil(h_total/4). Must cover h_sync + h_bp + h_act.</t>
         </is>
       </c>
     </row>
@@ -3743,14 +3822,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0x0018</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG0</t>
+          <t>APB_ADDR_OTF_CFG1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3758,29 +3837,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>8:4</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>meta_base_format</t>
+          <t>otf_cfg_h_sync</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metadata/base format configuration</t>
+          <t>OTF H_SYNC</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Usually issued with start in the same write</t>
+          <t>Horizontal sync width in pixels. RTL converts to OTF beats with ceil(h_sync/4).</t>
         </is>
       </c>
     </row>
@@ -3790,14 +3869,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0x001c</t>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG1</t>
+          <t>APB_ADDR_OTF_CFG2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3805,29 +3884,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[31:0]</t>
+          <t>otf_cfg_h_bp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Low 32 bits of the RGBA or Y metadata base address</t>
+          <t>OTF H_BP</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t>Horizontal back porch in pixels. RTL converts to OTF beats with ceil(h_bp/4). Active window starts after h_sync + h_bp.</t>
         </is>
       </c>
     </row>
@@ -3837,14 +3916,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>0x0020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG2</t>
+          <t>APB_ADDR_OTF_CFG2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3852,29 +3931,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[63:32]</t>
+          <t>otf_cfg_h_act</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>High 32 bits of the RGBA or Y metadata base address</t>
+          <t>OTF H_ACT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Horizontal active width in pixels. Usually program the visible output width; should match otf_cfg_img_width unless blanking/active width is intentionally different.</t>
         </is>
       </c>
     </row>
@@ -3884,14 +3963,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>0x0024</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG3</t>
+          <t>APB_ADDR_OTF_CFG3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3899,29 +3978,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[31:0]</t>
+          <t>otf_cfg_v_total</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV metadata base address</t>
+          <t>OTF V_TOTAL</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t>Vertical total in lines. Must cover v_sync + v_bp + v_act.</t>
         </is>
       </c>
     </row>
@@ -3931,14 +4010,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0x0028</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG4</t>
+          <t>APB_ADDR_OTF_CFG3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3946,29 +4025,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[63:32]</t>
+          <t>otf_cfg_v_sync</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV metadata base address</t>
+          <t>OTF V_SYNC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Vertical sync width in lines.</t>
         </is>
       </c>
     </row>
@@ -3978,14 +4057,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0x002c</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG5</t>
+          <t>APB_ADDR_OTF_CFG4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3993,7 +4072,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -4005,17 +4084,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>meta_tile_x_numbers</t>
+          <t>otf_cfg_v_bp</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metadata tile count in the horizontal direction</t>
+          <t>OTF V_BP</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t>Vertical back porch in lines. Active window starts after v_sync + v_bp.</t>
         </is>
       </c>
     </row>
@@ -4025,14 +4104,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>0x002c</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG5</t>
+          <t>APB_ADDR_OTF_CFG4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4040,7 +4119,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -4052,17 +4131,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>meta_tile_y_numbers</t>
+          <t>otf_cfg_v_act</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metadata tile count in the vertical direction</t>
+          <t>OTF V_ACT</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t>Vertical active height in lines. Program the visible output height.</t>
         </is>
       </c>
     </row>
@@ -4072,14 +4151,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>0x0030</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG0</t>
+          <t>APB_ADDR_META_CFG0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4087,7 +4166,7 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
@@ -4099,17 +4178,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>otf_cfg_img_width</t>
+          <t>meta_tile_x_numbers</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valid output image width in pixels</t>
+          <t>Y/RGBA metadata tile columns</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t>YUV420 UV metadata columns are derived by format. ceil(a/b) means round up division.</t>
         </is>
       </c>
     </row>
@@ -4119,14 +4198,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>0x0030</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG0</t>
+          <t>APB_ADDR_META_CFG0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4134,29 +4213,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>otf_cfg_format</t>
+          <t>meta_tile_y_numbers</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Output OTF format</t>
+          <t>Y/RGBA metadata tile rows</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t>For YUV420, UV metadata rows are derived internally as round_up(meta_tile_y_numbers/2).</t>
         </is>
       </c>
     </row>
@@ -4166,14 +4245,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0x0034</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>0x0030</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG1</t>
+          <t>REG_META_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4181,29 +4260,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>otf_cfg_h_total</t>
+          <t>meta_base_addr_rgba_y[31:0]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>OTF H_TOTAL</t>
+          <t>Low 32 bits of the RGBA or Y metadata base address</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t>For contiguous UBWC buffer, program Y/RGBA metadata start address. Metadata size formula: meta_pitch=align_up(ceil(plane_width/tile_w),64); meta_size=align_up(meta_pitch*align_up(ceil(plane_height/tile_h),16),4KB). Example NV12 1996x1074 base=0xA00000: Y meta_base=0xA00000, Y meta_pitch=64, Y meta_size=0x3000.</t>
         </is>
       </c>
     </row>
@@ -4213,14 +4292,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>0x0034</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG1</t>
+          <t>REG_META_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4228,29 +4307,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>otf_cfg_h_sync</t>
+          <t>meta_base_addr_rgba_y[63:32]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>OTF H_SYNC</t>
+          <t>High 32 bits of the RGBA or Y metadata base address</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t>Write after REG_META_BASE_Y_LO to complete this 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4260,14 +4339,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>0x0038</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG2</t>
+          <t>REG_TILE_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4275,29 +4354,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>otf_cfg_h_bp</t>
+          <t>tile_base_addr_rgba_y[31:0]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>OTF H_BP</t>
+          <t>Low 32 bits of the RGBA or Y compressed tile base address</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t>For YUV formats, program Y pixel/tile data start. Example NV12 1996x1074: Y tile_base = Y_meta_base + Y_meta_size = 0xA00000 + 0x3000 = 0xA03000.</t>
         </is>
       </c>
     </row>
@@ -4307,14 +4386,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0x0038</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG2</t>
+          <t>REG_TILE_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4322,29 +4401,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>otf_cfg_h_act</t>
+          <t>tile_base_addr_rgba_y[63:32]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>OTF H_ACT</t>
+          <t>High 32 bits of the RGBA or Y compressed tile base address</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t/>
+          <t>Write after REG_TILE_BASE_Y_LO to complete this 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4354,14 +4433,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0x003c</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>0x0040</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG3</t>
+          <t>REG_META_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4369,29 +4448,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>otf_cfg_v_total</t>
+          <t>meta_base_addr_uv[31:0]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>OTF V_TOTAL</t>
+          <t>Low 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t>For YUV formats, program UV metadata start address. Example NV12 1996x1074 contiguous layout: meta_base_uv = tile_base_y + Y_pixel_size = 0xA03000 + 0x220000 = 0xC23000.</t>
         </is>
       </c>
     </row>
@@ -4401,14 +4480,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0x003c</t>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>0x0044</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG3</t>
+          <t>REG_META_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4416,29 +4495,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>otf_cfg_v_sync</t>
+          <t>meta_base_addr_uv[63:32]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>OTF V_SYNC</t>
+          <t>High 32 bits of the UV metadata base address</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t>Write after REG_META_BASE_UV_LO to complete this 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4448,14 +4527,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>0x0040</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>0x0048</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG4</t>
+          <t>REG_TILE_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4463,29 +4542,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>otf_cfg_v_bp</t>
+          <t>tile_base_addr_uv[31:0]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>OTF V_BP</t>
+          <t>Low 32 bits of the UV compressed tile base address</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t>For YUV formats, program UV pixel/tile data start. RGBA format does not use this address.</t>
         </is>
       </c>
     </row>
@@ -4495,14 +4574,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0x0040</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG4</t>
+          <t>REG_TILE_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4510,29 +4589,29 @@
           <t>RW</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>otf_cfg_v_act</t>
+          <t>tile_base_addr_uv[63:32]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>OTF V_ACT</t>
+          <t>High 32 bits of the UV compressed tile base address</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t/>
+          <t>Write after REG_TILE_BASE_UV_LO to complete this 64-bit base address. RGBA format does not use this address.</t>
         </is>
       </c>
     </row>
@@ -4542,44 +4621,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>0x0044</t>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_BASE0</t>
+          <t>APB_ADDR_STATUS0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_uv[31:0]</t>
+          <t>frame_active</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Low 32 bits of the RGBA or UV tile base address</t>
+          <t>Whether the current frame is active</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t/>
+          <t>Set to 1 after start; cleared to 0 when the current frame fully completes</t>
         </is>
       </c>
     </row>
@@ -4589,44 +4668,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>0x0048</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_BASE1</t>
+          <t>APB_ADDR_STATUS0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_uv[63:32]</t>
+          <t>meta_busy</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>High 32 bits of the RGBA or UV tile base address</t>
+          <t>Metadata read stage busy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4636,39 +4715,39 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>0x004c</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_BASE2</t>
+          <t>APB_ADDR_STATUS0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tile_base_addr_y[31:0]</t>
+          <t>tile_busy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y tile base address</t>
+          <t>Tile read stage busy</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4683,44 +4762,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>0x0050</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_BASE3</t>
+          <t>APB_ADDR_STATUS0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tile_base_addr_y[63:32]</t>
+          <t>vivo_busy</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y tile base address</t>
+          <t>ubwc_dec_vivo_top busy</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4730,9 +4809,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>0x0054</t>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4752,22 +4831,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>frame_active</t>
+          <t>otf_busy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Whether the current frame is active</t>
+          <t>tile_to_otf stage busy</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Set to 1 after start; cleared to 0 when the current frame fully completes</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4777,9 +4856,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>0x0054</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4799,22 +4878,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>meta_busy</t>
+          <t>all_stage_idle</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metadata read stage busy</t>
+          <t>All current busy inputs are 0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t>May be 1 before start and after completion</t>
         </is>
       </c>
     </row>
@@ -4824,9 +4903,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>0x0054</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4846,22 +4925,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tile_busy</t>
+          <t>frame_idle_done</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tile read stage busy</t>
+          <t>No current busy and frame_active=0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t/>
+          <t>Recommended to combine with STATUS1[4] to judge frame completion</t>
         </is>
       </c>
     </row>
@@ -4871,14 +4950,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>0x0054</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS0</t>
+          <t>APB_ADDR_STATUS1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4886,29 +4965,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>vivo_busy</t>
+          <t>meta_done</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ubwc_dec_vivo_top busy</t>
+          <t>Metadata stage completed</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4918,14 +4997,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>0x0054</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS0</t>
+          <t>APB_ADDR_STATUS1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4933,29 +5012,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>otf_busy</t>
+          <t>tile_done</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>tile_to_otf stage busy</t>
+          <t>Tile stage completed</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -4965,14 +5044,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>0x0054</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS0</t>
+          <t>APB_ADDR_STATUS1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4980,29 +5059,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>all_stage_idle</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>All current busy inputs are 0</t>
+          <t>Reserved; reads 0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>May be 1 before start and after completion</t>
+          <t>VIVO completion is not latched as a done condition</t>
         </is>
       </c>
     </row>
@@ -5012,14 +5091,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>0x0054</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS0</t>
+          <t>APB_ADDR_STATUS1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5027,29 +5106,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>frame_idle_done</t>
+          <t>otf_done</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>No current busy and frame_active=0</t>
+          <t>OTF output stage completed</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Recommended to combine with STATUS1[4] to judge frame completion</t>
+          <t>Cleared when a new frame starts</t>
         </is>
       </c>
     </row>
@@ -5059,9 +5138,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5074,29 +5153,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>meta_done</t>
+          <t>frame_done</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metadata stage completed</t>
+          <t>Full-frame completion flag</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Most recommended software polling bit</t>
         </is>
       </c>
     </row>
@@ -5106,9 +5185,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5121,29 +5200,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tile_done</t>
+          <t>meta_seen_busy</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tile stage completed</t>
+          <t>Metadata stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Used to avoid falsely judging done before start</t>
         </is>
       </c>
     </row>
@@ -5153,9 +5232,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5168,29 +5247,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>vivo_done</t>
+          <t>tile_seen_busy</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>VIVO stage completed</t>
+          <t>Tile stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -5200,9 +5279,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5215,29 +5294,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>otf_done</t>
+          <t>vivo_seen_busy</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>OTF output stage completed</t>
+          <t>VIVO stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -5247,9 +5326,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5262,29 +5341,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>frame_done</t>
+          <t>otf_seen_busy</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Full-frame completion flag</t>
+          <t>OTF stage entered busy during this frame</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Most recommended software polling bit</t>
+          <t>Same as above</t>
         </is>
       </c>
     </row>
@@ -5294,14 +5373,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>0x0058</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_STATUS2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5311,27 +5390,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6:0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>meta_seen_busy</t>
+          <t>vivo_idle_bits</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metadata stage entered busy during this frame</t>
+          <t>Raw ubwc_dec_vivo_top idle bitmap</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Used to avoid falsely judging done before start</t>
+          <t>Passed through as o_idle[6:0] for software debug</t>
         </is>
       </c>
     </row>
@@ -5341,14 +5420,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_STATUS3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5358,27 +5437,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6:0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>tile_seen_busy</t>
+          <t>vivo_error_bits</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tile stage entered busy during this frame</t>
+          <t>Raw ubwc_dec_vivo_top error bitmap</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Passed through as o_error[6:0] for software debug</t>
         </is>
       </c>
     </row>
@@ -5388,44 +5467,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RW/W1P</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>vivo_seen_busy</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>VIVO stage entered busy during this frame</t>
+          <t>IRQ enable</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Defaults to 1 after reset</t>
         </is>
       </c>
     </row>
@@ -5435,44 +5514,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>0x0058</t>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>otf_seen_busy</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>OTF stage entered busy during this frame</t>
+          <t>IRQ clear pulse</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Writing 1 generates an irq_clear pulse in the AXI clock domain; readback is 0</t>
         </is>
       </c>
     </row>
@@ -5482,14 +5561,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>0x005c</t>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS2</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5504,22 +5583,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>vivo_idle_bits</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Raw ubwc_dec_vivo_top idle bitmap</t>
+          <t>IRQ pending status</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Passed through as o_idle[6:0] for software debug</t>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
@@ -5529,14 +5608,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>0x0060</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS3</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5551,22 +5630,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>vivo_error_bits</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Raw ubwc_dec_vivo_top error bitmap</t>
+          <t>Error IRQ pending status</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Passed through as o_error[6:0] for software debug</t>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
@@ -5576,9 +5655,9 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>0x0064</t>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5588,32 +5667,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RW/W1P</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>IRQ enable</t>
+          <t>Correct/frame IRQ pending status</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
@@ -5623,44 +5702,44 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>0x0064</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STATUS4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>W1P</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IRQ clear pulse</t>
+          <t>Bit0 any IRQ, bit1 error IRQ, bit2 correct IRQ</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Writing 1 generates an irq_clear pulse in the AXI clock domain; readback is 0</t>
+          <t>Synchronized into PCLK domain</t>
         </is>
       </c>
     </row>
@@ -5670,14 +5749,14 @@
           <t>ubwc_dec_apb_reg_blk</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>0x0064</t>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STAT_META</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5692,27 +5771,1965 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>stat_meta_tile_cnt</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Metadata valid tile count</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Current or last frame debug counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>0x006c</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STAT_TILE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>stat_tile_addr_cnt</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tile address valid tile count</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Current or last frame debug counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>0x0070</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STAT_OTF_TILE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>stat_otf_tile_cnt</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Tile-to-OTF accepted tile count</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Current or last frame debug counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>0x0074</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STAT_OTF_LINE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>stat_otf_line_cnt</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>OTF output line count</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Current or last frame debug counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ubwc_dec_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>0x0078</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>APB_ADDR_STAT_OTF_DE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>stat_otf_de_cnt</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>OTF output de &amp;&amp; ready beat count</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Current or last frame debug counter</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I64"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B13"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>UBWC ENC/DEC APB Configuration Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-07 04:34:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RTL sources</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>src/enc/ubwc_enc_apb_reg_blk.v; src/dec/ubwc_dec_apb_reg_blk.v</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Style reference</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rotation_apb_config.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ENC APB valid addresses</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>0x000,0x004,0x008,0x00C,0x010,0x014,0x018,0x01C,0x020,0x024,0x028,0x02C,0x030,0x034,0x038,0x03C,0x040,0x044,0x048,0x04C,0x050,0x054,0x058,0x05C,0x060,0x064,0x068,0x06C,0x070,0x074,0x078,0x07C,0x080,0x084,0x088,0x08C,0x090,0x094,0x098,0x09C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DEC APB valid addresses</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0x000,0x004,0x008,0x00C,0x010,0x014,0x018,0x01C,0x020,0x024,0x028,0x02C,0x030,0x034,0x038,0x03C,0x040,0x044,0x048,0x04C,0x050,0x054,0x058,0x05C,0x060,0x064,0x068,0x06C,0x070,0x074,0x078</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>APB alignment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>32-bit aligned accesses only; DEC may stall PREADY when the per-frame address path cannot accept a new write.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RGBA8888</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RGBA1010102</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>YUV420_8 / NV12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>irq_pending</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>IRQ pending status</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Synchronized into PCLK domain</t>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>YUV420_10 / P010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I60"/>
+  <autoFilter ref="A1:B13"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F46"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="110" customWidth="1"/>
+  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>配置频率</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>APB 操作</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>上电检查</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENC/DEC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>上电后一次</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>READ 0x000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>读取 VERSION，当前期望值为 0x00010000。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>上电检查</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ENC/DEC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>上电后一次</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>READ 0x004</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>读取 DATE。当前 ENC 为 0x20260406，DEC 为 0x20260403。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>中断初始化</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ENC/DEC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WRITE IRQ_CTRL[0]=1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。复位默认 irq_enable=1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>公共计算</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ENC/DEC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>软件计算 layout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>根据 format、width、height 计算 tile_w、tile_h、tile_cols、tile_rows、tile_pitch、meta_pitch 和各 plane base address。若只切换 frame buffer 地址，本步骤不需要重复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>公共计算</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ENC/DEC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>选择 format code</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0=RGBA8888，1=RGBA1010102，2=YUV420_8/NV12，3=YUV420_10/P010。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ENC 静态配置</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WRITE 0x00C REG_TILE_CFG1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>配置 four_line_format、lossy_rgba_2_1_format、tile_pitch。RGBA 写 four_line_format=1，YUV420 写 four_line_format=0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ENC 静态配置</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WRITE 0x008 REG_TILE_CFG0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>配置 ubwc_en、bank swizzle、bank spread。相同格式和 layout 的连续帧不需要重复写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ENC CI 配置</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WRITE 0x014/0x018/0x01C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>先写 CI_CFG1/2/3。保留 cfg bit 建议写 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ENC CI 配置</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WRITE 0x010 REG_ENC_CI_CFG0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>最后写 CI_CFG0，配置 enc_ci_input_type 和 enc_ci_alen。当前软件通常写 input_type=1、alen=7。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WRITE 0x024 REG_OTF_CFG1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>配置 width[15:0] 和 height[31:16]。连续帧尺寸不变时不需要重写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WRITE 0x028 REG_OTF_CFG2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420=32x8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WRITE 0x02C REG_OTF_CFG3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>配置 y_tile_cols 和 uv_tile_cols。RGBA: y=ceil(width/16), uv=0；YUV: y=ceil(width/32), uv=ceil(width/32)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>WRITE 0x050 REG_META_ACTIVE_SIZE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>配置 metadata active width/height。active 尺寸不变时不需要重写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WRITE 0x054 REG_META_PITCH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>配置 metadata pitch。宽度和格式不变时不需要重写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ENC 几何配置</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WRITE 0x020 REG_OTF_CFG0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>配置 otf_cfg_format。建议作为 OTF/metadata geometry 组的最后一笔写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ENC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WRITE 0x030/0x034</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>配置下一帧地址组的 Y metadata base 低/高 32 bit；RGBA 使用该槽位存 RGBA metadata。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ENC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WRITE 0x038/0x03C</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>配置下一帧地址组的 Y tile data base 低/高 32 bit；RGBA 使用该槽位存 RGBA tile data。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ENC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WRITE 0x040/0x044</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>配置 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ENC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WRITE 0x048</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>配置 UV tile data base 低 32 bit，RGBA 写 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ENC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WRITE 0x04C REG_TILE_BASE_UV_HI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。本写入会提交当前四个 64 bit base address 为一组帧地址，必须最后写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ENC 启动</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>每帧</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Start OTF input stream</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ENC 没有 APB start。上游 OTF vsync/hsync/de/data 进入后开始处理；fcnt[0] 用于选择地址 slot 和 sideband。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ENC 监控</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>READ 0x058/0x05C/0x060/0x064</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应地址 slot 未配置。IRQ bit 区分 correct/error pending。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ENC 清中断</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>软件处理中断后</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WRITE 0x060 bit[1]=1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DEC 静态配置</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WRITE 0x008 APB_ADDR_TILE_CFG0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>配置 bank swizzle、bank spread、4-line format、lossy_rgba_2_1_format。这些配置在 frame start 时锁存到 AXI 域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DEC 静态配置</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WRITE 0x00C APB_ADDR_TILE_CFG1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>配置 tile_cfg_pitch，单位 16 byte。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DEC CI 配置</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WRITE 0x010 APB_ADDR_TILE_CFG2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>配置 CI input type、sideband、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DEC VIVO 配置</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WRITE 0x014 APB_ADDR_VIVO_CFG</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>配置 vivo_ubwc_en 和 vivo_sreset。通常 vivo_ubwc_en 复位后保持 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DEC 几何配置</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WRITE 0x018 APB_ADDR_OTF_CFG0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>配置输出 img_width 和 format，同时更新 meta_base_format。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DEC OTF timing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WRITE 0x01C/0x020</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>配置 h_total、h_sync、h_bp、h_act。输出 timing 不变时连续帧不需要重写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEC OTF timing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WRITE 0x024/0x028</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>配置 v_total、v_sync、v_bp、v_act。输出 timing 不变时连续帧不需要重写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEC 几何配置</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>图像格式发生变化时配置</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WRITE 0x02C APB_ADDR_META_CFG0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>配置 Y/RGBA 基准 metadata tile_x_numbers 和 tile_y_numbers；YUV420 的 UV metadata tile 数由格式内部推导。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WRITE 0x030 then 0x034</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>配置 RGBA/Y metadata base 低/高 32 bit。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>WRITE 0x038 then 0x03C</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>配置 RGBA/Y compressed tile base 低/高 32 bit。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WRITE 0x040 then 0x044</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>配置 UV metadata base 低/高 32 bit。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DEC 每帧地址</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>每帧都要配置</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WRITE 0x048 then 0x04C</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>配置 UV compressed tile base 低/高 32 bit，RGBA 图像不关心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DEC 自动启动</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>硬件自动</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>不需要 APB start</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>完整地址组有效、metadata 不 busy、launch slot 可用时，硬件自动锁存本帧地址，产生 frame_start 并启动 decode。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DEC 监控</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>READ 0x050/0x054/0x060/0x064</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS4。STATUS1[4] 是 frame_done。STATUS4/IRQ_CTRL 区分 correct/error pending。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DEC 统计</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>运行中调试</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>READ 0x068/0x06C/0x070/0x074/0x078</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>读取 metadata tile count、tile address count、OTF tile count、OTF line count、OTF de beat count。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEC 清中断</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>软件处理中断后</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WRITE 0x060 bit[1]=1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>清除 DEC 中断 pending。VIVO idle/error 状态和统计计数仍可读。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>格式</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>tile_w</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>tile_h</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>bpp</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>配置复用说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RGBA8888</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>格式和尺寸不变时，tile/OTF/meta geometry 可复用；每帧只更新 base address。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RGBA1010102</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>几何规则同 RGBA8888；只换 buffer 地址时不需要重配 geometry。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>YUV420_8/NV12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1(Y),2(UV pair)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Y/UV 有独立 metadata/tile base；新 buffer 必须写每帧地址。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>YUV420_10/P010</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2(Y),4(UV pair)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>tile count 规则按 P010 tile_h=4 计算，pitch 使用 16 bit component 存储计算。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F46"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B10"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Address map</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APB registers are 32-bit word aligned. ENC defined range is 0x000..0x09C. DEC defined range is 0x000..0x078.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ENC address slots</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Two alternating address slots hold frame address sets for fcnt[0]=0/1. Each entry contains Y metadata base, Y tile base, UV metadata base, and UV tile base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ENC address commit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DEC address set</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Software writes metadata/tile bases for RGBA/Y and UV. A complete address set is required for each frame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DEC auto start</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A decode frame starts automatically when a complete DEC address set is valid, metadata is not busy, and the metadata launch slot is free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Contiguous UBWC layout</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>For YUV: Y metadata, Y tile data, UV metadata, UV tile data. For RGBA: RGBA metadata and RGBA tile data are enough; unused Y/UV partner bases may be written 0 as required by the wrapper path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Metadata pitch</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>meta_pitch=align_up(ceil(plane_width/tile_w),64). Metadata size aligns meta_pitch*align_up(tile_rows,16) to 4KB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tile pitch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tile_pitch register is in 16-byte units. pixel_pitch=align_up(width*bpp,tile_w*4*bpp); tile_pitch=pixel_pitch/16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IRQ timing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Correct IRQ is produced near the output hsync of the 4th line before frame end. Error IRQ is produced when an error condition is latched.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I79"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -166,12 +166,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IP version</t>
+          <t>IP version register.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h0001_0000</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -213,12 +213,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL date</t>
+          <t>RTL date register.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h2026_0406</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -260,12 +260,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Enable UBWC encoding</t>
+          <t>Encoder UBWC enable.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the tile address configuration group</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -307,12 +307,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Level-1 bank swizzle enable</t>
+          <t>Level-1 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -354,12 +354,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Level-2 bank swizzle enable</t>
+          <t>Level-2 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -401,12 +401,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Level-3 bank swizzle enable</t>
+          <t>Level-3 bank swizzle enable.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -448,12 +448,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Highest bank bit configuration</t>
+          <t>Highest bank bit.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bank spread enable</t>
+          <t>Bank spread enable.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4-line tile format enable</t>
+          <t>4-line tile format enable. RGBA=1, YUV420=0.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=1; YUV420_8/YUV420_10=0. Recommended to write this register before committing REG_TILE_CFG0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy format select</t>
+          <t>RGBA8888 lossy 2:1 layout select.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tile pitch in 16-byte units</t>
+          <t>Tile pitch in 16-byte units. RTL exports {1'b0, bits[26:16]}.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Write pitch_reg=align_up(width*bytes_per_pixel, tile_w*4*bytes_per_pixel)/16. bytes_per_pixel: RGBA8888=4, RGBA1010102=4, YUV420_8=1, YUV420_10=2. This register value is in 16-byte units, not bytes; effective field width is 11 bits. Example NV12 1996x1074: align_up(1996*1,32*4*1)=2048 bytes, tile_pitch=2048/16=128.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Encoded CI input type</t>
+          <t>CI input type. Current encoder software should write 1.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Encoding: 0=linear data, 1=tiled data. Fixed value for current encoder path: software should write 1. Recommended as the final write in the CI configuration group.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Encoded CI alen configuration</t>
+          <t>CI ALEN setting. Current software writes 3'd7.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Fixed value. Software should write 3'd7.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG0</t>
+          <t>REG_ENC_CI_CFG1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>enc_ci_lossy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>CI lossy enable.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0; current encoder format is configured by REG_OTF_CFG0.otf_cfg_format.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG0</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -814,22 +814,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>enc_ci_ubwc_cfg_0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0; forced PCM is generated dynamically by the OTF path.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG1</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SB_WIDTH-1:0</t>
+          <t>5:3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>enc_ci_sb</t>
+          <t>enc_ci_ubwc_cfg_1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG1</t>
+          <t>REG_ENC_CI_CFG2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9:6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>enc_ci_lossy</t>
+          <t>enc_ci_ubwc_cfg_2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Encoded CI lossy enable</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -955,22 +955,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_0</t>
+          <t>enc_ci_ubwc_cfg_3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5:3</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_1</t>
+          <t>enc_ci_ubwc_cfg_4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9:6</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_2</t>
+          <t>enc_ci_ubwc_cfg_5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_3</t>
+          <t>enc_ci_ubwc_cfg_6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1143,22 +1143,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>25:24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_4</t>
+          <t>enc_ci_ubwc_cfg_7</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1190,22 +1190,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>27:26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_5</t>
+          <t>enc_ci_ubwc_cfg_8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>30:28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_6</t>
+          <t>enc_ci_ubwc_cfg_9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_ENC_CI_CFG3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1284,22 +1284,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25:24</t>
+          <t>5:0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_7</t>
+          <t>enc_ci_ubwc_cfg_10</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_ENC_CI_CFG3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1331,22 +1331,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27:26</t>
+          <t>13:8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_8</t>
+          <t>enc_ci_ubwc_cfg_11</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Reserved UBWC CI configuration; software writes 0.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG2</t>
+          <t>REG_OTF_CFG0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30:28</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_9</t>
+          <t>otf_cfg_format</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input format: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>0x001c</t>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG3</t>
+          <t>REG_OTF_CFG1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_10</t>
+          <t>otf_cfg_width</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input image width in pixels.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>0x001c</t>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>REG_ENC_CI_CFG3</t>
+          <t>REG_OTF_CFG1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1472,22 +1472,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13:8</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>enc_ci_ubwc_cfg_11</t>
+          <t>otf_cfg_height</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reserved</t>
+          <t>Input/stored image height in pixels.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>0x0020</t>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG0</t>
+          <t>REG_OTF_CFG2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1519,22 +1519,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>otf_cfg_format</t>
+          <t>otf_cfg_tile_w</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Input OTF format</t>
+          <t>Tile width in pixels. RGBA=16, YUV420=32.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Recommended as the final write in the OTF configuration group. Format code: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>0x0024</t>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG1</t>
+          <t>REG_OTF_CFG2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>otf_cfg_width</t>
+          <t>otf_cfg_tile_h</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Input image width in pixels</t>
+          <t>Tile height in pixels. RGBA=4, NV12=8, P010=4.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Software should use this width to calculate tile columns: ceil(width / tile_w).</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>0x0024</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG1</t>
+          <t>REG_OTF_CFG3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>otf_cfg_height</t>
+          <t>otf_cfg_y_tile_cols</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Input image height in pixels</t>
+          <t>Y tile column count. RGBA formats use this field for RGBA tile columns.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Program stored/input frame height. For YUV420, UV plane uses half-height internally.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>0x0028</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG2</t>
+          <t>REG_OTF_CFG3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>otf_cfg_tile_w</t>
+          <t>otf_cfg_uv_tile_cols</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tile width in pixels</t>
+          <t>UV tile column count. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=16; YUV420_8/YUV420_10=32.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>0x0028</t>
+          <t>0x0030</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG2</t>
+          <t>REG_META_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1707,22 +1707,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>otf_cfg_tile_h</t>
+          <t>meta_y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tile height in pixels</t>
+          <t>Y metadata base address low word. RGBA formats use this slot for RGBA metadata.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Program by format: RGBA8888/RGBA1010102=4; YUV420_8/YUV420_10=8.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0x002c</t>
+          <t>0x0034</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG3</t>
+          <t>REG_META_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1754,22 +1754,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>otf_cfg_y_tile_cols</t>
+          <t>meta_y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Y tile column count</t>
+          <t>Y metadata base address high word. RGBA formats use this slot for RGBA metadata.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Program by format: RGBA formats=ceil(width/16); YUV formats Y=ceil(width/32).</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>0x002c</t>
+          <t>0x0038</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REG_OTF_CFG3</t>
+          <t>REG_TILE_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1801,22 +1801,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>otf_cfg_uv_tile_cols</t>
+          <t>y_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UV tile column count</t>
+          <t>Y compressed tile/pixel data base address low word. RGBA formats use this slot for RGBA data.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Program by format: RGBA formats=0; YUV formats UV=ceil(width/32).</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>0x0030</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_LO</t>
+          <t>REG_TILE_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y metadata base address</t>
+          <t>Y compressed tile/pixel data base address high word. RGBA formats use this slot for RGBA data.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>For RGBA formats, use this slot for RGBA metadata. For YUV formats, program Y metadata start. Example NV12 1996x1074 base=0xA00000: Y meta_base=0xA00000, Y meta_pitch=64, Y meta_size=0x3000.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>0x0034</t>
+          <t>0x0040</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_HI</t>
+          <t>REG_META_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y metadata base address</t>
+          <t>UV metadata base address low word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>0x0038</t>
+          <t>0x0044</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_LO</t>
+          <t>REG_META_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Low 32 bits of the Y compressed data base address</t>
+          <t>UV metadata base address high word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>For RGBA formats, use this slot for RGBA compressed data. For YUV formats, program Y pixel/tile data start. Example NV12 1996x1074: Y tile_base=0xA03000.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>0x003c</t>
+          <t>0x0048</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_HI</t>
+          <t>REG_TILE_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr[31:0]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>High 32 bits of the Y compressed data base address</t>
+          <t>UV compressed tile/pixel data base address low word. RGBA formats write 0.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>0x0040</t>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_LO</t>
+          <t>REG_TILE_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr[63:32]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV metadata base address</t>
+          <t>UV compressed tile/pixel data base address high word. Writing this register commits the current four base addresses as one frame address set.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV_meta_base=0xC23000.</t>
+          <t>Per-frame configuration. This high-word write must be last and commits the four base addresses as one frame address group.</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>0x0044</t>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_HI</t>
+          <t>REG_META_ACTIVE_SIZE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2083,22 +2083,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>meta_active_width_px</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV metadata base address</t>
+          <t>Metadata active width in pixels.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address when AXI_AW=64</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>0x0048</t>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_LO</t>
+          <t>REG_META_ACTIVE_SIZE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2130,22 +2130,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>meta_active_height_px</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV compressed data base address</t>
+          <t>Metadata active height in pixels.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>For RGBA formats, write 0. Example NV12 1996x1074: UV tile_base=0xC25000.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>0x004c</t>
+          <t>0x0054</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_HI</t>
+          <t>REG_META_PITCH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>meta_data_plane_pitch</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV compressed data base address</t>
+          <t>Metadata plane pitch configuration.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Forms the full 64-bit address and commits the current frame address set</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -2204,42 +2204,42 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>0x0050</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>REG_META_ACTIVE_SIZE</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>meta_active_width_px</t>
+          <t>enc_idle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metadata active-area width in pixels</t>
+          <t>Encoder idle input.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Writing 0 means using the full-frame width</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2251,42 +2251,42 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0x0050</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>REG_META_ACTIVE_SIZE</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>meta_active_height_px</t>
+          <t>enc_error</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metadata active-area height in pixels</t>
+          <t>Encoder error input.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Program metadata active height in pixels.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2298,42 +2298,42 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REG_META_PITCH</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>meta_data_plane_pitch</t>
+          <t>otf_to_tile_busy</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metadata plane pitch</t>
+          <t>OTF-to-tile stage busy.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Write meta_data_plane_pitch=align_up((align_up(width, tile_w*4)+tile_w-1)/tile_w, 64), matching ubwc_demo.cpp. Current encoder meta address path uses meta_data_plane_pitch&lt;&lt;4 as byte stride. Example NV12 1996x1074 Y plane: align_up((align_up(1996,128)+32-1)/32,64)=64. UV plane example from contiguous layout also uses meta_pitch=64.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2365,22 +2365,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>enc_idle</t>
+          <t>otf_to_tile_overflow</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Encoder core idle status</t>
+          <t>OTF-to-tile FIFO overflow.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>enc_error</t>
+          <t>otf_err_bline</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Encoder core error status</t>
+          <t>Bad-line error.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2459,22 +2459,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>otf_to_tile_busy</t>
+          <t>otf_err_bframe</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>OTF-to-tile busy status</t>
+          <t>Bad-frame error.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2506,22 +2506,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>otf_to_tile_overflow</t>
+          <t>meta_err_0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OTF-to-tile FIFO overflow status</t>
+          <t>Metadata error bit 0.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2553,22 +2553,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>otf_err_bline</t>
+          <t>meta_err_1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>OTF input bad-line error status</t>
+          <t>Metadata error bit 1.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2600,22 +2600,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>otf_err_bframe</t>
+          <t>frame_done</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>OTF input bad-frame error status</t>
+          <t>Frame done status from wrapper.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2647,22 +2647,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>meta_err_0</t>
+          <t>addr_cfg_invalid</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metadata generator error 0 status</t>
+          <t>Current frame needs an address slot that is not configured.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Currently tied low</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2694,22 +2694,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>meta_err_1</t>
+          <t>addr_cfg_valid0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metadata generator error 1 status</t>
+          <t>Address slot 0 has a configured entry.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Currently tied low</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2741,22 +2741,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>frame_done</t>
+          <t>addr_cfg_valid1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Encoder frame done status</t>
+          <t>Address slot 1 has a configured entry.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Live frame done input from wrapper</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RW/W1P</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IRQ enable</t>
+          <t>Interrupt enable.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>IRQ clear pulse</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Writing 1 generates an irq_clear pulse in the encoder clock domain; readback is 0</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -2939,24 +2939,870 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>IRQ pending status</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>irq_correct_pending</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Correct/frame-done interrupt pending.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>irq_error_pending</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Error interrupt pending.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>0x0060</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>REG_IRQ_CTRL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>0x0064</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REG_STATUS2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>irq_status</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>0x0068</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>REG_META_COUNT0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>meta_count0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>0x006c</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>REG_META_COUNT1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>meta_count1</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>0x0070</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>REG_TILEADDR_COUNT0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>tileaddr_count0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>0x0074</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>REG_TILEADDR_COUNT1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>tileaddr_count1</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>0x0078</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>REG_OTF_TILE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>otf_tile_count0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>0x007c</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>REG_OTF_TILE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>otf_tile_count1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>0x0080</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>REG_OTF_DE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>otf_de_count0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>0x0084</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>REG_OTF_DE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>otf_de_count1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>0x0088</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>REG_OTF_LINE_COUNT0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>otf_line_count0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>0x008c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>REG_OTF_LINE_COUNT1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>otf_line_count1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>0x0090</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>0x0094</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>0x009c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I61"/>
+  <autoFilter ref="A1:I79"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I59"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3055,12 +3901,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IP version</t>
+          <t>IP version register.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h0001_0000</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3948,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RTL date</t>
+          <t>RTL date register.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Returns fixed value 32'h2026_0403</t>
+          <t>Read once after reset to confirm software/RTL compatibility.</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3995,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Level-1 bank swizzle enable</t>
+          <t>Level-1 bank swizzle enable; stored for readback.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Software default writes 0. Combined bank swizzle default [2:0]=3'b110.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3196,12 +4042,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Level-2 bank swizzle enable</t>
+          <t>Level-2 bank swizzle enable; latched to AXI domain at frame start.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Software default writes 1. Combined bank swizzle default [2:0]=3'b110.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3243,12 +4089,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Level-3 bank swizzle enable</t>
+          <t>Level-3 bank swizzle enable; latched to AXI domain at frame start.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Software default writes 1. Combined bank swizzle default [2:0]=3'b110.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3290,12 +4136,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Highest bank bit configuration</t>
+          <t>Highest bank bit.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t/>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3337,12 +4183,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bank spread enable</t>
+          <t>Bank spread enable.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Software default writes 1.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3374,22 +4220,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tile_cfg_is_lossy_rgba_2_1_format</t>
+          <t>tile_cfg_4line_format</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>RGBA 2:1 lossy format select</t>
+          <t>4-line tile format; stored for readback.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Only applies to RGBA8888 metadata/tile address path. 0=normal RGBA/lossless layout, 1=RGBA8888 lossy 2:1 layout. When 1, decoder halves the effective tile_y for address calculation, adds a 128-byte offset for odd tile_y, disables bank spread for this path, and treats 256-byte metadata payload as 128 bytes.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3401,12 +4247,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0x000c</t>
+          <t>0x0008</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG1</t>
+          <t>APB_ADDR_TILE_CFG0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3421,22 +4267,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11:0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tile_cfg_pitch</t>
+          <t>tile_cfg_is_lossy_rgba_2_1_format</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tile pitch configuration</t>
+          <t>RGBA8888 lossy 2:1 layout select.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tile surface pitch in 16-byte units. Program tile_cfg_pitch=align_up(width*bpp, tile_w*4*bpp)/16. bpp: RGBA8888/RGBA1010102=4, YUV420_8=1, YUV420_10=2. tile_w: RGBA=16, YUV=32. RTL uses tile_cfg_pitch&lt;&lt;4 as byte pitch. Example NV12 1996x1074: align_up(1996*1,32*4*1)=2048 bytes, tile_cfg_pitch=2048/16=128.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3448,12 +4294,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x000c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APB_ADDR_TILE_CFG2</t>
+          <t>APB_ADDR_TILE_CFG1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3468,22 +4314,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11:0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_input_type</t>
+          <t>tile_cfg_pitch</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CI input type</t>
+          <t>Tile pitch in 16-byte units.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0=linear data, 1=tiled data. Software default writes 1.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3515,22 +4361,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_lossy</t>
+          <t>tile_cfg_ci_input_type</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CI lossy enable</t>
+          <t>CI input type. Software should write 1 for tiled CI.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Software writes 1 for lossy format and 0 for lossless format.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3562,22 +4408,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10:9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tile_cfg_ci_alpha_mode</t>
+          <t>tile_cfg_ci_lossy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI alpha mode configuration</t>
+          <t>CI lossy enable.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reserved. Software should write 0.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3589,12 +4435,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>APB_ADDR_VIVO_CFG</t>
+          <t>APB_ADDR_TILE_CFG2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3604,27 +4450,27 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10:9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>vivo_ubwc_en</t>
+          <t>tile_cfg_ci_alpha_mode</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ubwc_dec_vivo_top enable</t>
+          <t>CI alpha mode.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3656,22 +4502,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vivo_sreset</t>
+          <t>vivo_ubwc_en</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>VIVO submodule soft reset</t>
+          <t>VIVO UBWC path enable.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Can be used to independently clear VIVO internal state</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3683,12 +4529,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG0</t>
+          <t>APB_ADDR_VIVO_CFG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3703,22 +4549,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>otf_cfg_img_width</t>
+          <t>vivo_sreset</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valid output image width in pixels</t>
+          <t>VIVO soft reset.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Program active image width in pixels. Used to limit line unpacking: RGBA words=ceil(width/4), YUV420_8/NV12 words=ceil(width/16), YUV420_10/P010 words=ceil(width/8).</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3750,22 +4596,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>otf_cfg_format</t>
+          <t>otf_cfg_img_width</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Output OTF format</t>
+          <t>Valid output image width in pixels.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Frame-level output format. Codes: 0=RGBA8888, 1=RGBA1010102, 2=YUV420_8/NV12, 3=YUV420_10/P010. Also drives meta_base_format.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3777,12 +4623,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>0x001c</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG1</t>
+          <t>APB_ADDR_OTF_CFG0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3797,22 +4643,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>otf_cfg_h_total</t>
+          <t>otf_cfg_format</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OTF H_TOTAL</t>
+          <t>Output OTF format; also drives meta_base_format.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Horizontal total in pixels. RTL converts to OTF beats with ceil(h_total/4). Must cover h_sync + h_bp + h_act.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3844,22 +4690,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>otf_cfg_h_sync</t>
+          <t>otf_cfg_h_total</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OTF H_SYNC</t>
+          <t>Horizontal total.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Horizontal sync width in pixels. RTL converts to OTF beats with ceil(h_sync/4).</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3871,12 +4717,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0x0020</t>
+          <t>0x001c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG2</t>
+          <t>APB_ADDR_OTF_CFG1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3891,22 +4737,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>otf_cfg_h_bp</t>
+          <t>otf_cfg_h_sync</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>OTF H_BP</t>
+          <t>Horizontal sync width.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Horizontal back porch in pixels. RTL converts to OTF beats with ceil(h_bp/4). Active window starts after h_sync + h_bp.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3938,22 +4784,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>otf_cfg_h_act</t>
+          <t>otf_cfg_h_bp</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>OTF H_ACT</t>
+          <t>Horizontal back porch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Horizontal active width in pixels. Usually program the visible output width; should match otf_cfg_img_width unless blanking/active width is intentionally different.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -3965,12 +4811,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>0x0024</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG3</t>
+          <t>APB_ADDR_OTF_CFG2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3985,22 +4831,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>otf_cfg_v_total</t>
+          <t>otf_cfg_h_act</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>OTF V_TOTAL</t>
+          <t>Horizontal active width.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vertical total in lines. Must cover v_sync + v_bp + v_act.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4032,22 +4878,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>otf_cfg_v_sync</t>
+          <t>otf_cfg_v_total</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>OTF V_SYNC</t>
+          <t>Vertical total.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Vertical sync width in lines.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4905,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>0x0028</t>
+          <t>0x0024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>APB_ADDR_OTF_CFG4</t>
+          <t>APB_ADDR_OTF_CFG3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4079,22 +4925,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>otf_cfg_v_bp</t>
+          <t>otf_cfg_v_sync</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>OTF V_BP</t>
+          <t>Vertical sync width.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Vertical back porch in lines. Active window starts after v_sync + v_bp.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4126,22 +4972,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>otf_cfg_v_act</t>
+          <t>otf_cfg_v_bp</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OTF V_ACT</t>
+          <t>Vertical back porch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Vertical active height in lines. Program the visible output height.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4999,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0x002c</t>
+          <t>0x0028</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>APB_ADDR_META_CFG0</t>
+          <t>APB_ADDR_OTF_CFG4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4173,22 +5019,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>meta_tile_x_numbers</t>
+          <t>otf_cfg_v_act</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Y/RGBA metadata tile columns</t>
+          <t>Vertical active height.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>YUV420 UV metadata columns are derived by format. ceil(a/b) means round up division.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4220,22 +5066,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31:16</t>
+          <t>15:0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>meta_tile_y_numbers</t>
+          <t>meta_tile_x_numbers</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Y/RGBA metadata tile rows</t>
+          <t>Y/RGBA metadata tile columns; YUV420 UV columns are derived by format.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>For YUV420, UV metadata rows are derived internally as round_up(meta_tile_y_numbers/2).</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4247,12 +5093,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0x0030</t>
+          <t>0x002c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_LO</t>
+          <t>APB_ADDR_META_CFG0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4267,22 +5113,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>31:16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[31:0]</t>
+          <t>meta_tile_y_numbers</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Low 32 bits of the RGBA or Y metadata base address</t>
+          <t>Y/RGBA metadata tile rows; YUV420 UV rows are derived internally.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>For contiguous UBWC buffer, program Y/RGBA metadata start address. Metadata size formula: meta_pitch=align_up(ceil(plane_width/tile_w),64); meta_size=align_up(meta_pitch*align_up(ceil(plane_height/tile_h),16),4KB). Example NV12 1996x1074 base=0xA00000: Y meta_base=0xA00000, Y meta_pitch=64, Y meta_size=0x3000.</t>
+          <t>Configure when image format, size, layout, or timing changes. Reuse when only frame buffer addresses change.</t>
         </is>
       </c>
     </row>
@@ -4294,12 +5140,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>0x0034</t>
+          <t>0x0030</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REG_META_BASE_Y_HI</t>
+          <t>REG_META_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4319,17 +5165,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[63:32]</t>
+          <t>meta_base_addr_rgba_y[31:0]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>High 32 bits of the RGBA or Y metadata base address</t>
+          <t>RGBA/Y metadata base address low word.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Write after REG_META_BASE_Y_LO to complete this 64-bit base address.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4341,12 +5187,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>0x0038</t>
+          <t>0x0034</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_LO</t>
+          <t>REG_META_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4366,17 +5212,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[31:0]</t>
+          <t>meta_base_addr_rgba_y[63:32]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Low 32 bits of the RGBA or Y compressed tile base address</t>
+          <t>RGBA/Y metadata base address high word.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>For YUV formats, program Y pixel/tile data start. Example NV12 1996x1074: Y tile_base = Y_meta_base + Y_meta_size = 0xA00000 + 0x3000 = 0xA03000.</t>
+          <t>Per-frame configuration. Low/high words complete this base address.</t>
         </is>
       </c>
     </row>
@@ -4388,12 +5234,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>0x003c</t>
+          <t>0x0038</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_Y_HI</t>
+          <t>REG_TILE_BASE_Y_LO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4413,17 +5259,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[63:32]</t>
+          <t>tile_base_addr_rgba_y[31:0]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>High 32 bits of the RGBA or Y compressed tile base address</t>
+          <t>RGBA/Y compressed tile data base address low word.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Write after REG_TILE_BASE_Y_LO to complete this 64-bit base address.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4435,12 +5281,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>0x0040</t>
+          <t>0x003c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_LO</t>
+          <t>REG_TILE_BASE_Y_HI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4460,17 +5306,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[31:0]</t>
+          <t>tile_base_addr_rgba_y[63:32]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV metadata base address</t>
+          <t>RGBA/Y compressed tile data base address high word.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>For YUV formats, program UV metadata start address. Example NV12 1996x1074 contiguous layout: meta_base_uv = tile_base_y + Y_pixel_size = 0xA03000 + 0x220000 = 0xC23000.</t>
+          <t>Per-frame configuration. Low/high words complete this base address.</t>
         </is>
       </c>
     </row>
@@ -4482,12 +5328,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>0x0044</t>
+          <t>0x0040</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REG_META_BASE_UV_HI</t>
+          <t>REG_META_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4507,17 +5353,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[63:32]</t>
+          <t>meta_base_addr_uv[31:0]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV metadata base address</t>
+          <t>UV metadata base address low word.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Write after REG_META_BASE_UV_LO to complete this 64-bit base address.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4529,12 +5375,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>0x0048</t>
+          <t>0x0044</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_LO</t>
+          <t>REG_META_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4554,17 +5400,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[31:0]</t>
+          <t>meta_base_addr_uv[63:32]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Low 32 bits of the UV compressed tile base address</t>
+          <t>UV metadata base address high word.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>For YUV formats, program UV pixel/tile data start. RGBA format does not use this address.</t>
+          <t>Per-frame configuration. Low/high words complete this base address.</t>
         </is>
       </c>
     </row>
@@ -4576,12 +5422,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>0x004c</t>
+          <t>0x0048</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>REG_TILE_BASE_UV_HI</t>
+          <t>REG_TILE_BASE_UV_LO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4601,17 +5447,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[63:32]</t>
+          <t>tile_base_addr_uv[31:0]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>High 32 bits of the UV compressed tile base address</t>
+          <t>UV compressed tile data base address low word. RGBA format does not use this address.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Write after REG_TILE_BASE_UV_LO to complete this 64-bit base address. RGBA format does not use this address.</t>
+          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
         </is>
       </c>
     </row>
@@ -4623,42 +5469,42 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>0x0050</t>
+          <t>0x004c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS0</t>
+          <t>REG_TILE_BASE_UV_HI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>frame_active</t>
+          <t>tile_base_addr_uv[63:32]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Whether the current frame is active</t>
+          <t>UV compressed tile data base address high word. RGBA format does not use this address.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Set to 1 after start; cleared to 0 when the current frame fully completes</t>
+          <t>Per-frame configuration. Low/high words complete this base address.</t>
         </is>
       </c>
     </row>
@@ -4690,22 +5536,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>meta_busy</t>
+          <t>frame_active</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metadata read stage busy</t>
+          <t>Current frame active.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t/>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -4737,22 +5583,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tile_busy</t>
+          <t>meta_busy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tile read stage busy</t>
+          <t>Metadata stage busy.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -4784,22 +5630,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>vivo_busy</t>
+          <t>tile_busy</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ubwc_dec_vivo_top busy</t>
+          <t>Tile address/read stage busy.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -4831,22 +5677,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>otf_busy</t>
+          <t>vivo_busy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>tile_to_otf stage busy</t>
+          <t>VIVO stage busy.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t/>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -4878,22 +5724,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>all_stage_idle</t>
+          <t>otf_busy</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All current busy inputs are 0</t>
+          <t>Tile-to-OTF stage busy.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>May be 1 before start and after completion</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -4925,22 +5771,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>frame_idle_done</t>
+          <t>all_stage_idle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>No current busy and frame_active=0</t>
+          <t>No current busy stage.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Recommended to combine with STATUS1[4] to judge frame completion</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -4952,12 +5798,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0050</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_STATUS0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4965,29 +5811,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>meta_done</t>
+          <t>frame_idle_done</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metadata stage completed</t>
+          <t>No busy stage and frame_active=0.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -5012,29 +5858,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4:0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tile_done</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tile stage completed</t>
+          <t>Done bitmap: bit0 meta, bit1 tile address, bit2 reserved, bit3 otf, bit4 frame.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -5059,29 +5905,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8:5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>stage_seen</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Reserved; reads 0</t>
+          <t>Stage-seen-busy bitmap for meta/tile/vivo/otf.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>VIVO completion is not latched as a done condition</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -5093,12 +5939,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_STATUS2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5106,29 +5952,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6:0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>otf_done</t>
+          <t>vivo_idle_bits</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>OTF output stage completed</t>
+          <t>Raw VIVO idle bitmap.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cleared when a new frame starts</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -5140,12 +5986,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_STATUS3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5153,29 +5999,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6:0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>frame_done</t>
+          <t>vivo_error_bits</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Full-frame completion flag</t>
+          <t>Raw VIVO error bitmap.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Most recommended software polling bit</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -5187,42 +6033,42 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0x00000000</t>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>meta_seen_busy</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metadata stage entered busy during this frame</t>
+          <t>Interrupt enable.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Used to avoid falsely judging done before start</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -5234,17 +6080,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>W1P</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5254,22 +6100,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>tile_seen_busy</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tile stage entered busy during this frame</t>
+          <t>Write 1 to clear latched correct/error interrupt status.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -5281,12 +6127,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5294,29 +6140,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>vivo_seen_busy</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>VIVO stage entered busy during this frame</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5328,12 +6174,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>0x0054</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS1</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5341,29 +6187,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>otf_seen_busy</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>OTF stage entered busy during this frame</t>
+          <t>Error interrupt pending.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Same as above</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5375,12 +6221,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>0x0058</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS2</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5395,22 +6241,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>vivo_idle_bits</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Raw ubwc_dec_vivo_top idle bitmap</t>
+          <t>Correct/frame interrupt pending.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Passed through as o_idle[6:0] for software debug</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5422,42 +6268,42 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS3</t>
+          <t>APB_ADDR_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>vivo_error_bits</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Raw ubwc_dec_vivo_top error bitmap</t>
+          <t>Write 1 after one full input UBWC address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Passed through as o_error[6:0] for software debug</t>
+          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
         </is>
       </c>
     </row>
@@ -5469,42 +6315,42 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STATUS4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RW/W1P</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>IRQ enable</t>
+          <t>Bit0 any IRQ, bit1 error IRQ, bit2 correct IRQ.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Defaults to 1 after reset</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5516,42 +6362,42 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STAT_META</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>W1P</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>stat_meta_tile_cnt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>IRQ clear pulse</t>
+          <t>Metadata valid tile count for the current/last frame.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Writing 1 generates an irq_clear pulse in the AXI clock domain; readback is 0</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5563,12 +6409,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STAT_TILE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5583,22 +6429,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>stat_tile_addr_cnt</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>IRQ pending status</t>
+          <t>Tile address generator valid tile count.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5610,12 +6456,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STAT_OTF_TILE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5630,22 +6476,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>stat_otf_tile_cnt</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Error IRQ pending status</t>
+          <t>Tile-to-OTF accepted tile count.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5657,12 +6503,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APB_ADDR_IRQ_CTRL</t>
+          <t>APB_ADDR_STAT_OTF_LINE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5677,22 +6523,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>stat_otf_line_cnt</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Correct/frame IRQ pending status</t>
+          <t>OTF output line count.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -5704,12 +6550,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APB_ADDR_STATUS4</t>
+          <t>APB_ADDR_STAT_OTF_DE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5724,262 +6570,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>31:0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>stat_otf_de_cnt</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 error IRQ, bit2 correct IRQ</t>
+          <t>OTF output data-enable beat count.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Synchronized into PCLK domain</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ubwc_dec_apb_reg_blk</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>0x0068</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>APB_ADDR_STAT_META</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>31:0</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>stat_meta_tile_cnt</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Metadata valid tile count</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Current or last frame debug counter</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ubwc_dec_apb_reg_blk</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>0x006c</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>APB_ADDR_STAT_TILE</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>31:0</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>stat_tile_addr_cnt</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Tile address valid tile count</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Current or last frame debug counter</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ubwc_dec_apb_reg_blk</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>0x0070</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>APB_ADDR_STAT_OTF_TILE</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>31:0</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stat_otf_tile_cnt</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Tile-to-OTF accepted tile count</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Current or last frame debug counter</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ubwc_dec_apb_reg_blk</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>0x0074</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>APB_ADDR_STAT_OTF_LINE</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>31:0</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>stat_otf_line_cnt</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>OTF output line count</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Current or last frame debug counter</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ubwc_dec_apb_reg_blk</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>0x0078</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>APB_ADDR_STAT_OTF_DE</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>31:0</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>stat_otf_de_cnt</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>OTF output de &amp;&amp; ready beat count</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Current or last frame debug counter</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6008,7 +6619,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-07 04:34:29</t>
+          <t>2026-05-14 22:08:50</t>
         </is>
       </c>
     </row>
@@ -6532,7 +7143,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420=32x8。</t>
+          <t>配置 tile_w 和 tile_h。RGBA=16x4，YUV420_8=32x8，YUV420_10=32x4。</t>
         </is>
       </c>
     </row>
@@ -6847,12 +7458,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start OTF input stream</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENC 没有 APB start。上游 OTF vsync/hsync/de/data 进入后开始处理；fcnt[0] 用于选择地址 slot 和 sideband。</t>
+          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7623,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、sideband、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7918,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEC 自动启动</t>
+          <t>DEC 启动</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7317,7 +7928,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>硬件自动</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7327,12 +7938,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>不需要 APB start</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>完整地址组有效、metadata 不 busy、launch slot 可用时，硬件自动锁存本帧地址，产生 frame_start 并启动 decode。</t>
+          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
@@ -7652,7 +8263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value.</t>
+          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value. A separate IRQ_CTRL[5] start write is still required for the frame.</t>
         </is>
       </c>
     </row>
@@ -7664,19 +8275,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Software writes metadata/tile bases for RGBA/Y and UV. A complete address set is required for each frame.</t>
+          <t>Software writes metadata/tile bases for RGBA/Y and UV. A complete address set plus a separate IRQ_CTRL[5] start write is required for each frame.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEC auto start</t>
+          <t>DEC start token</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A decode frame starts automatically when a complete DEC address set is valid, metadata is not busy, and the metadata launch slot is free.</t>
+          <t>A decode frame starts when a complete DEC address set and a START token are both valid, metadata is not busy, and the metadata launch slot is free.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +8335,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Correct IRQ is produced near the output hsync of the 4th line before frame end. Error IRQ is produced when an error condition is latched.</t>
+          <t>Correct IRQ/frame_done is produced after the final valid frame output/data completion event. Error IRQ is produced when an error condition is latched.</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metadata error bit 0.</t>
+          <t>Metadata co-buffer overflow error.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metadata error bit 1.</t>
+          <t>Metadata tile-order error.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2788,22 +2788,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>addr_cfg_overflow</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap.</t>
+          <t>Address slot FIFO overflow sticky status.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Read during runtime.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2815,42 +2815,42 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>0x00000001</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>rst_drain_timeout</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Interrupt enable.</t>
+          <t>AXI drain timeout during encoder soft reset.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Configure after reset or when the interrupt policy changes.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2862,42 +2862,42 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>W1P</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Write 1 after software handles the interrupt; readback is 0.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>0x00000001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Any pending interrupt.</t>
+          <t>Interrupt enable.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -2966,32 +2966,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Correct/frame-done interrupt pending.</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Error interrupt pending.</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3060,32 +3060,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>W1P</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+          <t>Correct/frame-done interrupt pending.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>Error interrupt pending.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3144,42 +3144,42 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>W1P</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3755,47 +3755,141 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
+          <t>0x0094</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>REG_TILE_AXI_W_CNT1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>dynamic</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>dynamic</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5959,17 +6053,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>vivo_idle_bits</t>
+          <t>vivo_idle</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Raw VIVO idle bitmap.</t>
+          <t>VIVO idle status.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6006,17 +6100,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6:0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>vivo_error_bits</t>
+          <t>vivo_error</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Raw VIVO error bitmap.</t>
+          <t>VIVO error status.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6619,7 +6713,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-14 22:08:50</t>
+          <t>2026-05-19 09:33:12</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CI input type. Current encoder software should write 1.</t>
+          <t>CI input type. 1=tiled data, 0=linear data. Register reset is 0; software should write 1 for the normal tiled UBWC path.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CI ALEN setting. Current software writes 3'd7.</t>
+          <t>CI ALEN setting. Register reset is 0; software should write 7 for the normal VIVO_ENC configuration.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[31:0]</t>
+          <t>meta_y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>meta_y_base_offset_addr[63:32]</t>
+          <t>meta_y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[31:0]</t>
+          <t>y_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>y_base_offset_addr[63:32]</t>
+          <t>y_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[31:0]</t>
+          <t>meta_uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>meta_uv_base_offset_addr[63:32]</t>
+          <t>meta_uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[31:0]</t>
+          <t>uv_base_offset_addr_31_0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>uv_base_offset_addr[63:32]</t>
+          <t>uv_base_offset_addr_63_32</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2217,9 +2217,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2264,9 +2264,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2311,9 +2311,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2358,9 +2358,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2405,9 +2405,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2452,9 +2452,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2499,9 +2499,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2546,9 +2546,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2593,9 +2593,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2640,9 +2640,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Current frame needs an address slot that is not configured.</t>
+          <t>Sticky current-slot address-not-configured error. The ENC data path selects address slot0 or slot1 from the current frame fcnt[0]. When hardware checks the current slot address validity and the selected address FIFO is empty, active_addr_cfg_valid is 0, this bit is set and held, and the condition contributes to error IRQ. This means the current frame has no usable META/TILE base addresses. Software must submit the per-frame address group for the corresponding slot, confirm that the software buffer queue is aligned with fcnt[0], then clear the sticky status with REG_IRQ_CTRL[1] irq_clear; disabling enc_ubwc_en or hard reset also clears it.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2687,9 +2687,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2734,9 +2734,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2781,9 +2781,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Address slot FIFO overflow sticky status.</t>
+          <t>Sticky address-configuration FIFO overflow status. One frame address group contains four 64-bit base addresses: META Y, TILE Y, META UV, and TILE UV. Software commits one address group by writing REG_TILE_BASE_UV_HI. The APB block alternates committed groups into slot0/slot1 address FIFOs; each slot FIFO depth is 4. If the selected slot FIFO is full when the commit write occurs, the current address group is not pushed, this bit is set and held, and the condition contributes to error IRQ. Software should stop submitting new address groups, wait for existing frames to consume FIFO entries, clear the sticky bit with REG_IRQ_CTRL[1] irq_clear, and make sure the software buffer queue is aligned with the hardware address queue; if needed, disable enc_ubwc_en and reconfigure.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2828,9 +2828,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AXI drain timeout during encoder soft reset.</t>
+          <t>Sticky AXI drain timeout during encoder soft reset. Before asserting the internal soft reset, ENC stops issuing new AXI writes and waits for tile/meta AXI write outstanding transactions to drain. If idle is not reached within 16'hffff i_axi_clk cycles, this bit is set and held until REG_IRQ_CTRL[1] irq_clear or hard reset.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2875,9 +2875,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Interrupt enable.</t>
+          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3016,9 +3016,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3063,9 +3063,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3110,9 +3110,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3191,42 +3191,42 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>vsync_reset_en</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>When set, an input OTF VSYNC rising edge requests an encoder soft reset through the AXI-drain reset sequencer and re-arms the frame start token after reset release.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Configure according to the system policy. When set, ENC input VSYNC rising edges trigger a soft reset and re-arm frame start.</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3251,29 +3251,29 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3298,9 +3298,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3345,9 +3345,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3392,9 +3392,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3439,9 +3439,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3486,9 +3486,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3533,9 +3533,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3580,9 +3580,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3627,9 +3627,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3674,9 +3674,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3721,9 +3721,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3768,9 +3768,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3815,9 +3815,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3849,47 +3849,94 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>dynamic</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4465,7 +4512,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CI input type. Software should write 1 for tiled CI.</t>
+          <t>CI input type. 1=tiled data, 0=linear data. Register reset is 0; software should write 1 for the normal tiled UBWC path.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4591,7 +4638,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4606,7 +4653,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>VIVO UBWC path enable.</t>
+          <t>VIVO UBWC path enable. Register reset is 0; software should write 1 before starting decode.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5259,7 +5306,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[31:0]</t>
+          <t>meta_base_addr_rgba_y_31_0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5306,7 +5353,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>meta_base_addr_rgba_y[63:32]</t>
+          <t>meta_base_addr_rgba_y_63_32</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5353,7 +5400,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[31:0]</t>
+          <t>tile_base_addr_rgba_y_31_0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5400,7 +5447,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tile_base_addr_rgba_y[63:32]</t>
+          <t>tile_base_addr_rgba_y_63_32</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5447,7 +5494,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[31:0]</t>
+          <t>meta_base_addr_uv_31_0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5494,7 +5541,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>meta_base_addr_uv[63:32]</t>
+          <t>meta_base_addr_uv_63_32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5541,7 +5588,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[31:0]</t>
+          <t>tile_base_addr_uv_31_0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5588,7 +5635,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tile_base_addr_uv[63:32]</t>
+          <t>tile_base_addr_uv_63_32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5623,9 +5670,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5670,9 +5717,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5717,9 +5764,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5764,9 +5811,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5811,9 +5858,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5858,9 +5905,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5905,9 +5952,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5952,9 +5999,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5999,9 +6046,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6046,9 +6093,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6093,9 +6140,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6142,7 +6189,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0x00000001</t>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6157,7 +6204,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Interrupt enable.</t>
+          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6234,9 +6281,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6281,9 +6328,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6328,9 +6375,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6422,9 +6469,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6469,9 +6516,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6516,9 +6563,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6563,9 +6610,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6610,9 +6657,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6657,9 +6704,9 @@
           <t>RO</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>dynamic</t>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6713,7 +6760,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 09:33:12</t>
+          <t>2026-05-21 13:09:24</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7028,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。复位默认 irq_enable=1。</t>
+          <t>使能中断。ENC IRQ_CTRL 地址为 0x060，DEC IRQ_CTRL 地址为 0x060。寄存器复位值为 0，软件需要写 1 才使能 IRQ。</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7220,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>最后写 CI_CFG0，配置 enc_ci_input_type 和 enc_ci_alen。当前软件通常写 input_type=1、alen=7。</t>
+          <t>最后写 CI_CFG0；寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 enc_ci_input_type=1、enc_ci_alen=7。</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7636,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应地址 slot 未配置。IRQ bit 区分 correct/error pending。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7764,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、lossy、alpha mode。当前 tiled UBWC 流通常写 input_type=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7796,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>配置 vivo_ubwc_en 和 vivo_sreset。通常 vivo_ubwc_en 复位后保持 1。</t>
+          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
         </is>
       </c>
     </row>

--- a/docs/ubwc_reg_tables.xlsx
+++ b/docs/ubwc_reg_tables.xlsx
@@ -67,7 +67,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Y metadata base address low word. RGBA formats use this slot for RGBA metadata.</t>
+          <t>Y metadata base address low word. RGBA formats use this field for RGBA metadata.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Y metadata base address high word. RGBA formats use this slot for RGBA metadata.</t>
+          <t>Y metadata base address high word. RGBA formats use this field for RGBA metadata.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Y compressed tile/pixel data base address low word. RGBA formats use this slot for RGBA data.</t>
+          <t>Y compressed tile/pixel data base address low word. RGBA formats use this field for RGBA data.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Y compressed tile/pixel data base address high word. RGBA formats use this slot for RGBA data.</t>
+          <t>Y compressed tile/pixel data base address high word. RGBA formats use this field for RGBA data.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Per-frame configuration. Low/high words form one 64-bit base address.</t>
+          <t>Configure when the address or layout changes. Low/high words form one 64-bit base address in the single address set.</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>UV compressed tile/pixel data base address high word. Writing this register commits the current four base addresses as one frame address set.</t>
+          <t>UV compressed tile/pixel data base address high word. Write this register last to mark the single working address set complete; START then latches it.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Per-frame configuration. This high-word write must be last and commits the four base addresses as one frame address group.</t>
+          <t>Configure when the address or layout changes. Write this high word last to mark the single address set complete, then issue START to latch it.</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sticky current-slot address-not-configured error. The ENC data path selects address slot0 or slot1 from the current frame fcnt[0]. When hardware checks the current slot address validity and the selected address FIFO is empty, active_addr_cfg_valid is 0, this bit is set and held, and the condition contributes to error IRQ. This means the current frame has no usable META/TILE base addresses. Software must submit the per-frame address group for the corresponding slot, confirm that the software buffer queue is aligned with fcnt[0], then clear the sticky status with REG_IRQ_CTRL[1] irq_clear; disabling enc_ubwc_en or hard reset also clears it.</t>
+          <t>Sticky single-address configuration error. It is set when the ENC data path checks an address configuration but the most recently START-latched META Y, TILE Y, META UV, and TILE UV base-address set is invalid. The condition contributes to error IRQ and remains set until REG_IRQ_CTRL[1] irq_clear, enc_ubwc_en disable, or hard reset.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>addr_cfg_valid0</t>
+          <t>addr_cfg_valid</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Address slot 0 has a configured entry.</t>
+          <t>The single META/TILE base-address set latched by the most recent START is valid. All frames reuse this set until software writes a new complete set and issues START again.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>addr_cfg_valid1</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Address slot 1 has a configured entry.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>addr_cfg_overflow</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sticky address-configuration FIFO overflow status. One frame address group contains four 64-bit base addresses: META Y, TILE Y, META UV, and TILE UV. Software commits one address group by writing REG_TILE_BASE_UV_HI. The APB block alternates committed groups into slot0/slot1 address FIFOs; each slot FIFO depth is 4. If the selected slot FIFO is full when the commit write occurs, the current address group is not pushed, this bit is set and held, and the condition contributes to error IRQ. Software should stop submitting new address groups, wait for existing frames to consume FIFO entries, clear the sticky bit with REG_IRQ_CTRL[1] irq_clear, and make sure the software buffer queue is aligned with the hardware address queue; if needed, disable enc_ubwc_en and reconfigure.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>0x005c</t>
+          <t>0x0058</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>REG_STATUS1</t>
+          <t>REG_STATUS0</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2882,22 +2882,22 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7:0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stage_done</t>
+          <t>cfg_valid</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Encoder stage done bitmap.</t>
+          <t>Result of the most recent START configuration commit. Set when format, geometry, tile/metadata parameters, and the single address set are valid. When clear, ENC holds o_otf_ready low.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Read during runtime.</t>
+          <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
@@ -2909,17 +2909,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>0x0060</t>
+          <t>0x005c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>REG_IRQ_CTRL</t>
+          <t>REG_STATUS1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7:0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>irq_enable</t>
+          <t>stage_done</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
+          <t>Encoder stage done bitmap.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Configure after reset or when the interrupt policy changes.</t>
+          <t>Read during runtime.</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>W1P</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2976,22 +2976,22 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>irq_clear</t>
+          <t>irq_enable</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
+          <t>Interrupt enable. Register reset is 0; software should write 1 when IRQ output is required.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Write 1 after software handles the interrupt; readback is 0.</t>
+          <t>Configure after reset or when the interrupt policy changes.</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>W1P</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3023,22 +3023,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>irq_pending</t>
+          <t>irq_clear</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Any pending interrupt.</t>
+          <t>Write 1 to generate an interrupt clear pulse; readback is 0.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>Write 1 after software handles the interrupt; readback is 0.</t>
         </is>
       </c>
     </row>
@@ -3070,17 +3070,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>irq_correct_pending</t>
+          <t>irq_pending</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Correct/frame-done interrupt pending.</t>
+          <t>Any pending interrupt.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3117,17 +3117,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>irq_error_pending</t>
+          <t>irq_correct_pending</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Error interrupt pending.</t>
+          <t>Correct/frame-done interrupt pending.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>W1P</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3164,22 +3164,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>irq_error_pending</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Write 1 after one full output address group has been configured. Address writes only fill the pending address queues; start is a separate frame token.</t>
+          <t>Error interrupt pending.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Write 1 after the per-frame address group is complete; readback is 0. Address writes do not start a frame by themselves.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>W1P</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>vsync_reset_en</t>
+          <t>start</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>When set, an input OTF VSYNC rising edge requests an encoder soft reset through the AXI-drain reset sequencer and re-arms the frame start token after reset release.</t>
+          <t>Write 1 to validate and latch the complete ENC configuration snapshot. START does not reset the frame pipeline and does not start OTF processing. It must complete before the target VSYNC; a late commit applies from the next VSYNC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Configure according to the system policy. When set, ENC input VSYNC rising edges trigger a soft reset and re-arm frame start.</t>
+          <t>Write after static configuration and the single address set are ready; then read STATUS0[14] cfg_valid and STATUS0[10] addr_cfg_valid. START does not start a frame.</t>
         </is>
       </c>
     </row>
@@ -3238,17 +3238,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>0x0064</t>
+          <t>0x0060</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REG_STATUS2</t>
+          <t>REG_IRQ_CTRL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2:0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>irq_status</t>
+          <t>Reserved</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
+          <t>Reserved; reads as 0.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Read during runtime or after interrupt handling for status/debug.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>0x0068</t>
+          <t>0x0064</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>REG_META_COUNT0</t>
+          <t>REG_STATUS2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3305,22 +3305,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>31:0</t>
+          <t>2:0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>meta_count0</t>
+          <t>irq_status</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>meta_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>Bit0 any IRQ, bit1 correct IRQ, bit2 error IRQ.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Read-only status or statistic information.</t>
+          <t>Read during runtime or after interrupt handling for status/debug.</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0x006c</t>
+          <t>0x0068</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>REG_META_COUNT1</t>
+          <t>REG_META_COUNT0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>meta_count1</t>
+          <t>meta_count0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>meta_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>0x0070</t>
+          <t>0x006c</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT0</t>
+          <t>REG_META_COUNT1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>tileaddr_count0</t>
+          <t>meta_count1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>tileaddr_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>meta_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>0x0074</t>
+          <t>0x0070</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>REG_TILEADDR_COUNT1</t>
+          <t>REG_TILEADDR_COUNT0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>tileaddr_count1</t>
+          <t>tileaddr_count0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>tileaddr_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>0x0078</t>
+          <t>0x0074</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT0</t>
+          <t>REG_TILEADDR_COUNT1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>otf_tile_count0</t>
+          <t>tileaddr_count1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>otf_tile_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tileaddr_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>0x007c</t>
+          <t>0x0078</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REG_OTF_TILE_COUNT1</t>
+          <t>REG_OTF_TILE_COUNT0</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>otf_tile_count1</t>
+          <t>otf_tile_count0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>otf_tile_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>0x0080</t>
+          <t>0x007c</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT0</t>
+          <t>REG_OTF_TILE_COUNT1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>otf_de_count0</t>
+          <t>otf_tile_count1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>otf_de_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_tile_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>0x0084</t>
+          <t>0x0080</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REG_OTF_DE_COUNT1</t>
+          <t>REG_OTF_DE_COUNT0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>otf_de_count1</t>
+          <t>otf_de_count0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>otf_de_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>0x0088</t>
+          <t>0x0084</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT0</t>
+          <t>REG_OTF_DE_COUNT1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>otf_line_count0</t>
+          <t>otf_de_count1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>otf_line_count0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_de_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>0x008c</t>
+          <t>0x0088</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REG_OTF_LINE_COUNT1</t>
+          <t>REG_OTF_LINE_COUNT0</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>otf_line_count1</t>
+          <t>otf_line_count0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>otf_line_count1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>0x0090</t>
+          <t>0x008c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT0</t>
+          <t>REG_OTF_LINE_COUNT1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0</t>
+          <t>otf_line_count1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>otf_line_count1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>0x0094</t>
+          <t>0x0090</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>REG_TILE_AXI_W_CNT1</t>
+          <t>REG_TILE_AXI_W_CNT0</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1</t>
+          <t>tile_axi_w_cnt0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>0x0098</t>
+          <t>0x0094</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REG_META_AXI_W_CNT0</t>
+          <t>REG_TILE_AXI_W_CNT1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0</t>
+          <t>tile_axi_w_cnt1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
+          <t>tile_axi_w_cnt1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3896,47 +3896,94 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
+          <t>0x0098</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>REG_META_AXI_W_CNT0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>31:0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt0 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Read-only status or statistic information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ubwc_enc_apb_reg_blk</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>0x009c</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>REG_META_AXI_W_CNT1</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>0x00000000</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>0x00000000</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>31:0</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>meta_axi_w_cnt1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 follows fcnt[0] address slot.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>meta_axi_w_cnt1 statistic counter; suffix 0/1 is the fcnt[0] statistics bucket and is independent of address selection.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Read-only status or statistic information.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I82"/>
+  <autoFilter ref="A1:I83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6760,7 +6807,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 13:09:24</t>
+          <t>2026-07-24 23:24:40</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6940,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -7419,7 +7466,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7429,7 +7476,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7444,14 +7491,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y metadata base 低/高 32 bit；RGBA 使用该槽位存 RGBA metadata。</t>
+          <t>配置唯一一组 Y metadata base 低/高 32 bit；RGBA 使用该位置存 RGBA metadata。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7461,7 +7508,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7476,14 +7523,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>配置下一帧地址组的 Y tile data base 低/高 32 bit；RGBA 使用该槽位存 RGBA tile data。</t>
+          <t>配置唯一一组 Y tile data base 低/高 32 bit；RGBA 使用该位置存 RGBA tile data。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7493,7 +7540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7508,14 +7555,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>配置 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV metadata base 低/高 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7525,7 +7572,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7540,14 +7587,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 低 32 bit，RGBA 写 0。</t>
+          <t>配置唯一一组 UV tile data base 低 32 bit，RGBA 写 0。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENC 每帧地址</t>
+          <t>ENC 单一地址</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7557,7 +7604,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>地址或 layout 变化时配置</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7572,14 +7619,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。本写入会提交当前四个 64 bit base address 为一组帧地址，必须最后写。</t>
+          <t>配置 UV tile data base 高 32 bit，RGBA 写 0。该寄存器必须最后写，用于标记唯一工作地址组完整。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENC 启动</t>
+          <t>ENC 配置提交</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7589,7 +7636,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>每帧</t>
+          <t>静态配置或地址快照变化时</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7604,14 +7651,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>写 START token。地址写入只填充地址队列，不再作为 start 标志；写 START 后再送入对应 OTF vsync/hsync/de/data。</t>
+          <t>写 START 提交并锁存完整配置快照。START 不复位也不启动帧；读取 STATUS0[14] cfg_valid。START 必须在目标 VSYNC 前完成。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENC 监控</t>
+          <t>ENC 帧启动</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7621,7 +7668,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>运行中</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -7631,19 +7678,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>READ 0x058/0x05C/0x060/0x064</t>
+          <t>输入 VSYNC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。addr_cfg_invalid 表示当前 fcnt[0] 对应 slot 没有可用地址配置，是 sticky 错误状态；软件补齐地址并确认队列对齐后，通过 REG_IRQ_CTRL[1] irq_clear 清除。IRQ bit 区分 correct/error pending。</t>
+          <t>每个 VSYNC 上升沿采样 cfg_valid，再触发 AXI drain 和全链路帧复位。采样有效时复位释放后自动运行；所有帧复用最近一次 START 锁存的唯一地址组。采样无效时整帧 o_otf_ready=0。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENC 清中断</t>
+          <t>ENC 监控</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7653,7 +7700,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>软件处理中断后</t>
+          <t>运行中</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7663,29 +7710,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WRITE 0x060 bit[1]=1</t>
+          <t>READ 0x058/0x05C/0x060/0x064</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS2。cfg_valid 表示 START 提交结果；addr_cfg_valid 表示唯一地址组已锁存且有效；IRQ bit 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEC 静态配置</t>
+          <t>ENC 清中断</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>ENC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>图像格式发生变化时配置</t>
+          <t>软件处理中断后</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7695,12 +7742,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WRITE 0x008 APB_ADDR_TILE_CFG0</t>
+          <t>WRITE 0x060 bit[1]=1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>配置 bank swizzle、bank spread、4-line format、lossy_rgba_2_1_format。这些配置在 frame start 时锁存到 AXI 域。</t>
+          <t>清除 ENC 中断 pending。统计计数仍可用于调试。</t>
         </is>
       </c>
     </row>
@@ -7727,19 +7774,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WRITE 0x00C APB_ADDR_TILE_CFG1</t>
+          <t>WRITE 0x008 APB_ADDR_TILE_CFG0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>配置 tile_cfg_pitch，单位 16 byte。</t>
+          <t>配置 bank swizzle、bank spread、4-line format、lossy_rgba_2_1_format。这些配置在 frame start 时锁存到 AXI 域。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEC CI 配置</t>
+          <t>DEC 静态配置</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7759,19 +7806,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WRITE 0x010 APB_ADDR_TILE_CFG2</t>
+          <t>WRITE 0x00C APB_ADDR_TILE_CFG1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
+          <t>配置 tile_cfg_pitch，单位 16 byte。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DEC VIVO 配置</t>
+          <t>DEC CI 配置</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7791,19 +7838,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WRITE 0x014 APB_ADDR_VIVO_CFG</t>
+          <t>WRITE 0x010 APB_ADDR_TILE_CFG2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
+          <t>配置 CI input type、lossy、alpha mode。寄存器复位值为 0，普通 tiled UBWC 路径软件应配置 ci_input_type=1。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEC 几何配置</t>
+          <t>DEC VIVO 配置</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7823,19 +7870,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WRITE 0x018 APB_ADDR_OTF_CFG0</t>
+          <t>WRITE 0x014 APB_ADDR_VIVO_CFG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>配置输出 img_width 和 format，同时更新 meta_base_format。</t>
+          <t>配置 vivo_ubwc_en 和 vivo_sreset。寄存器复位值为 0，启动 decode 前软件应配置 vivo_ubwc_en=1。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEC OTF timing</t>
+          <t>DEC 几何配置</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7855,12 +7902,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WRITE 0x01C/0x020</t>
+          <t>WRITE 0x018 APB_ADDR_OTF_CFG0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>配置 h_total、h_sync、h_bp、h_act。输出 timing 不变时连续帧不需要重写。</t>
+          <t>配置输出 img_width 和 format，同时更新 meta_base_format。</t>
         </is>
       </c>
     </row>
@@ -7887,19 +7934,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WRITE 0x024/0x028</t>
+          <t>WRITE 0x01C/0x020</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>配置 v_total、v_sync、v_bp、v_act。输出 timing 不变时连续帧不需要重写。</t>
+          <t>配置 h_total、h_sync、h_bp、h_act。输出 timing 不变时连续帧不需要重写。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEC 几何配置</t>
+          <t>DEC OTF timing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7919,19 +7966,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WRITE 0x02C APB_ADDR_META_CFG0</t>
+          <t>WRITE 0x024/0x028</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>配置 Y/RGBA 基准 metadata tile_x_numbers 和 tile_y_numbers；YUV420 的 UV metadata tile 数由格式内部推导。</t>
+          <t>配置 v_total、v_sync、v_bp、v_act。输出 timing 不变时连续帧不需要重写。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEC 每帧地址</t>
+          <t>DEC 几何配置</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7941,7 +7988,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>每帧都要配置</t>
+          <t>图像格式发生变化时配置</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7951,12 +7998,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WRITE 0x030 then 0x034</t>
+          <t>WRITE 0x02C APB_ADDR_META_CFG0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>配置 RGBA/Y metadata base 低/高 32 bit。</t>
+          <t>配置 Y/RGBA 基准 metadata tile_x_numbers 和 tile_y_numbers；YUV420 的 UV metadata tile 数由格式内部推导。</t>
         </is>
       </c>
     </row>
@@ -7983,12 +8030,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WRITE 0x038 then 0x03C</t>
+          <t>WRITE 0x030 then 0x034</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>配置 RGBA/Y compressed tile base 低/高 32 bit。</t>
+          <t>配置 RGBA/Y metadata base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8062,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WRITE 0x040 then 0x044</t>
+          <t>WRITE 0x038 then 0x03C</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>配置 UV metadata base 低/高 32 bit。</t>
+          <t>配置 RGBA/Y compressed tile base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
@@ -8047,19 +8094,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WRITE 0x048 then 0x04C</t>
+          <t>WRITE 0x040 then 0x044</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>配置 UV compressed tile base 低/高 32 bit，RGBA 图像不关心。</t>
+          <t>配置 UV metadata base 低/高 32 bit。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEC 启动</t>
+          <t>DEC 每帧地址</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8069,7 +8116,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>每帧</t>
+          <t>每帧都要配置</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8079,19 +8126,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WRITE 0x060 bit[5]=1</t>
+          <t>WRITE 0x048 then 0x04C</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
+          <t>配置 UV compressed tile base 低/高 32 bit，RGBA 图像不关心。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEC 监控</t>
+          <t>DEC 启动</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8101,7 +8148,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>运行中</t>
+          <t>每帧</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8111,19 +8158,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>READ 0x050/0x054/0x060/0x064</t>
+          <t>WRITE 0x060 bit[5]=1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS4。STATUS1[4] 是 frame_done。STATUS4/IRQ_CTRL 区分 correct/error pending。</t>
+          <t>写 START token。完整地址组和 START token 都有效，且 metadata stage 可接受新帧时，硬件锁存本帧地址并启动 decode。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEC 统计</t>
+          <t>DEC 监控</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8133,7 +8180,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>运行中调试</t>
+          <t>运行中</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8143,121 +8190,121 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>READ 0x068/0x06C/0x070/0x074/0x078</t>
+          <t>READ 0x050/0x054/0x060/0x064</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>读取 metadata tile count、tile address count、OTF tile count、OTF line count、OTF de beat count。</t>
+          <t>读取 STATUS0、STATUS1、IRQ_CTRL、STATUS4。STATUS1[4] 是 frame_done。STATUS4/IRQ_CTRL 区分 correct/error pending。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>DEC 统计</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>运行中调试</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>READ 0x068/0x06C/0x070/0x074/0x078</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>读取 metadata tile count、tile address count、OTF tile count、OTF line count、OTF de beat count。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>DEC 清中断</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>软件处理中断后</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>WRITE 0x060 bit[1]=1</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>清除 DEC 中断 pending。VIVO idle/error 状态和统计计数仍可读。</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>tile_w</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>tile_h</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>bpp</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>配置复用说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>RGBA8888</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>格式和尺寸不变时，tile/OTF/meta geometry 可复用；每帧只更新 base address。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RGBA1010102</t>
+          <t>RGBA8888</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8277,83 +8324,115 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>几何规则同 RGBA8888；只换 buffer 地址时不需要重配 geometry。</t>
+          <t>格式、尺寸和输出 buffer 不变时，静态配置与唯一地址组均可持续复用。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YUV420_8/NV12</t>
+          <t>RGBA1010102</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1(Y),2(UV pair)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Y/UV 有独立 metadata/tile base；新 buffer 必须写每帧地址。</t>
+          <t>几何规则同 RGBA8888；更换 buffer 地址后重新写完整地址组并写 START。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>YUV420_8/NV12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1(Y),2(UV pair)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Y/UV 使用唯一一组独立 metadata/tile base；地址变化后重新写完整地址组并写 START。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>YUV420_10/P010</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>2(Y),4(UV pair)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>tile count 规则按 P010 tile_h=4 计算，pitch 使用 16 bit component 存储计算。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F46"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
@@ -8387,12 +8466,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENC address slots</t>
+          <t>ENC single address set</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Two alternating address slots hold frame address sets for fcnt[0]=0/1. Each entry contains Y metadata base, Y tile base, UV metadata base, and UV tile base.</t>
+          <t>ENC has one address set containing Y metadata base, Y tile base, UV metadata base, and UV tile base. fcnt does not select an address.</t>
         </is>
       </c>
     </row>
@@ -8404,84 +8483,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Write REG_TILE_BASE_UV_HI @0x04C last. That write snapshots the current META_BASE_Y, TILE_BASE_Y, META_BASE_UV and the just-written TILE_BASE_UV value. A separate IRQ_CTRL[5] start write is still required for the frame.</t>
+          <t>Write REG_TILE_BASE_UV_HI @0x04C last to mark the working address set complete. Write IRQ_CTRL[5] START to validate and latch the complete snapshot, then check STATUS0[14] cfg_valid and STATUS0[10] addr_cfg_valid.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEC address set</t>
+          <t>ENC frame reset</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Software writes metadata/tile bases for RGBA/Y and UV. A complete address set plus a separate IRQ_CTRL[5] start write is required for each frame.</t>
+          <t>Every input VSYNC rising edge samples the committed configuration, requests AXI drain, and resets the frame pipeline. Processing starts automatically after reset release only when the sampled result is valid. Frames reuse the same latched addresses until a later START updates them.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEC start token</t>
+          <t>DEC address set</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A decode frame starts when a complete DEC address set and a START token are both valid, metadata is not busy, and the metadata launch slot is free.</t>
+          <t>Software writes metadata/tile bases for RGBA/Y and UV. A complete address set plus a separate IRQ_CTRL[5] start write is required for each frame.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Contiguous UBWC layout</t>
+          <t>DEC start token</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>For YUV: Y metadata, Y tile data, UV metadata, UV tile data. For RGBA: RGBA metadata and RGBA tile data are enough; unused Y/UV partner bases may be written 0 as required by the wrapper path.</t>
+          <t>A decode frame starts when a complete DEC address set and a START token are both valid, metadata is not busy, and the metadata launch slot is free.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Metadata pitch</t>
+          <t>Contiguous UBWC layout</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>meta_pitch=align_up(ceil(plane_width/tile_w),64). Metadata size aligns meta_pitch*align_up(tile_rows,16) to 4KB.</t>
+          <t>For YUV: Y metadata, Y tile data, UV metadata, UV tile data. For RGBA: RGBA metadata and RGBA tile data are enough; unused Y/UV partner bases may be written 0 as required by the wrapper path.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tile pitch</t>
+          <t>Metadata pitch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tile_pitch register is in 16-byte units. pixel_pitch=align_up(width*bpp,tile_w*4*bpp); tile_pitch=pixel_pitch/16.</t>
+          <t>meta_pitch=align_up(ceil(plane_width/tile_w),64). Metadata size aligns meta_pitch*align_up(tile_rows,16) to 4KB.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Tile pitch</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tile_pitch register is in 16-byte units. pixel_pitch=align_up(width*bpp,tile_w*4*bpp); tile_pitch=pixel_pitch/16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>IRQ timing</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Correct IRQ/frame_done is produced after the final valid frame output/data completion event. Error IRQ is produced when an error condition is latched.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>